--- a/artfynd/A 9045-2024 artfynd.xlsx
+++ b/artfynd/A 9045-2024 artfynd.xlsx
@@ -5684,10 +5684,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>117551193</v>
+        <v>117552948</v>
       </c>
       <c r="B43" t="n">
-        <v>56499</v>
+        <v>56503</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5700,30 +5700,26 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100138</v>
+        <v>102613</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="K43" t="inlineStr"/>
-      <c r="L43" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+      <c r="L43" t="inlineStr"/>
       <c r="M43" t="inlineStr">
         <is>
           <t>färsk spillning</t>
@@ -5732,14 +5728,14 @@
       <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Sumpskog NV Bredmossen, N kanten, Vg</t>
+          <t>Norrkant Ledningsmossen, Drängedalen, Vg</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>344129</v>
+        <v>343871</v>
       </c>
       <c r="R43" t="n">
-        <v>6434322</v>
+        <v>6434192</v>
       </c>
       <c r="S43" t="n">
         <v>25</v>
@@ -5771,7 +5767,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5781,12 +5777,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>09:10</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Stora skitar på två olika stenar.</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5813,10 +5804,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>117552948</v>
+        <v>117551193</v>
       </c>
       <c r="B44" t="n">
-        <v>56502</v>
+        <v>56500</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5829,26 +5820,30 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>102613</v>
+        <v>100138</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr"/>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M44" t="inlineStr">
         <is>
           <t>färsk spillning</t>
@@ -5857,14 +5852,14 @@
       <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Norrkant Ledningsmossen, Drängedalen, Vg</t>
+          <t>Sumpskog NV Bredmossen, N kanten, Vg</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>343871</v>
+        <v>344129</v>
       </c>
       <c r="R44" t="n">
-        <v>6434192</v>
+        <v>6434322</v>
       </c>
       <c r="S44" t="n">
         <v>25</v>
@@ -5896,7 +5891,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5906,7 +5901,12 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Stora skitar på två olika stenar.</t>
         </is>
       </c>
       <c r="AD44" t="b">

--- a/artfynd/A 9045-2024 artfynd.xlsx
+++ b/artfynd/A 9045-2024 artfynd.xlsx
@@ -6173,10 +6173,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>118756709</v>
+        <v>118755601</v>
       </c>
       <c r="B47" t="n">
-        <v>57148</v>
+        <v>5165</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -6185,50 +6185,47 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100100</v>
+        <v>102204</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Bivråk</t>
+          <t>Grönhjon</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Pernis apivorus</t>
+          <t>Callidium aeneum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(De Geer, 1775)</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr"/>
       <c r="K47" t="inlineStr"/>
       <c r="L47" t="inlineStr"/>
       <c r="M47" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Skog NO Ledningsmossen, Drängedalen, Vg</t>
+          <t>Kjolgran N Ledningsmossen, Drängedalen, Vg</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>343996</v>
+        <v>343953</v>
       </c>
       <c r="R47" t="n">
-        <v>6434225</v>
+        <v>6434253</v>
       </c>
       <c r="S47" t="n">
         <v>25</v>
@@ -6260,7 +6257,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -6270,12 +6267,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>12:05</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Rörde sig över Ledningsmossen, ropande.</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6284,6 +6276,7 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
+      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
@@ -6302,10 +6295,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>118756857</v>
+        <v>118756024</v>
       </c>
       <c r="B48" t="n">
-        <v>56502</v>
+        <v>57443</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6314,46 +6307,50 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100138</v>
+        <v>103021</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K48" t="inlineStr"/>
       <c r="L48" t="inlineStr"/>
       <c r="M48" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Häll 3 NV Bredmossen, Drängedalen, Vg</t>
+          <t>N om Ledningsmossen, Drängedalen, Vg</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>344067</v>
+        <v>343920</v>
       </c>
       <c r="R48" t="n">
-        <v>6434348</v>
+        <v>6434211</v>
       </c>
       <c r="S48" t="n">
         <v>25</v>
@@ -6385,7 +6382,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>07:45</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6395,7 +6392,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>07:55</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6422,10 +6419,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>118755601</v>
+        <v>118756709</v>
       </c>
       <c r="B49" t="n">
-        <v>5165</v>
+        <v>57148</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6434,47 +6431,50 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>102204</v>
+        <v>100100</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Grönhjon</t>
+          <t>Bivråk</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Callidium aeneum</t>
+          <t>Pernis apivorus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(De Geer, 1775)</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr"/>
-      <c r="J49" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K49" t="inlineStr"/>
       <c r="L49" t="inlineStr"/>
       <c r="M49" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Kjolgran N Ledningsmossen, Drängedalen, Vg</t>
+          <t>Skog NO Ledningsmossen, Drängedalen, Vg</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>343953</v>
+        <v>343996</v>
       </c>
       <c r="R49" t="n">
-        <v>6434253</v>
+        <v>6434225</v>
       </c>
       <c r="S49" t="n">
         <v>25</v>
@@ -6506,7 +6506,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6516,7 +6516,12 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>12:05</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Rörde sig över Ledningsmossen, ropande.</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6525,7 +6530,6 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
-      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
@@ -6544,10 +6548,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>118756024</v>
+        <v>118756857</v>
       </c>
       <c r="B50" t="n">
-        <v>57443</v>
+        <v>56502</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6556,50 +6560,46 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>103021</v>
+        <v>100138</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
       <c r="K50" t="inlineStr"/>
       <c r="L50" t="inlineStr"/>
       <c r="M50" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>N om Ledningsmossen, Drängedalen, Vg</t>
+          <t>Häll 3 NV Bredmossen, Drängedalen, Vg</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>343920</v>
+        <v>344067</v>
       </c>
       <c r="R50" t="n">
-        <v>6434211</v>
+        <v>6434348</v>
       </c>
       <c r="S50" t="n">
         <v>25</v>
@@ -6631,7 +6631,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>07:45</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6641,7 +6641,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>07:55</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AD50" t="b">

--- a/artfynd/A 9045-2024 artfynd.xlsx
+++ b/artfynd/A 9045-2024 artfynd.xlsx
@@ -6173,10 +6173,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>118755601</v>
+        <v>118756857</v>
       </c>
       <c r="B47" t="n">
-        <v>5165</v>
+        <v>56502</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -6185,47 +6185,46 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>102204</v>
+        <v>100138</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Grönhjon</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Callidium aeneum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(De Geer, 1775)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="J47" t="inlineStr"/>
       <c r="K47" t="inlineStr"/>
       <c r="L47" t="inlineStr"/>
       <c r="M47" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Kjolgran N Ledningsmossen, Drängedalen, Vg</t>
+          <t>Häll 3 NV Bredmossen, Drängedalen, Vg</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>343953</v>
+        <v>344067</v>
       </c>
       <c r="R47" t="n">
-        <v>6434253</v>
+        <v>6434348</v>
       </c>
       <c r="S47" t="n">
         <v>25</v>
@@ -6257,7 +6256,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -6267,7 +6266,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6276,7 +6275,6 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
-      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
@@ -6295,10 +6293,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>118756024</v>
+        <v>118756709</v>
       </c>
       <c r="B48" t="n">
-        <v>57443</v>
+        <v>57148</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6307,25 +6305,25 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>103021</v>
+        <v>100100</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Bivråk</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Pernis apivorus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -6337,20 +6335,20 @@
       <c r="L48" t="inlineStr"/>
       <c r="M48" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>N om Ledningsmossen, Drängedalen, Vg</t>
+          <t>Skog NO Ledningsmossen, Drängedalen, Vg</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>343920</v>
+        <v>343996</v>
       </c>
       <c r="R48" t="n">
-        <v>6434211</v>
+        <v>6434225</v>
       </c>
       <c r="S48" t="n">
         <v>25</v>
@@ -6382,7 +6380,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>07:45</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6392,7 +6390,12 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>07:55</t>
+          <t>12:05</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Rörde sig över Ledningsmossen, ropande.</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6419,10 +6422,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>118756709</v>
+        <v>118756024</v>
       </c>
       <c r="B49" t="n">
-        <v>57148</v>
+        <v>57443</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6431,25 +6434,25 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100100</v>
+        <v>103021</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Bivråk</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Pernis apivorus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -6461,20 +6464,20 @@
       <c r="L49" t="inlineStr"/>
       <c r="M49" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Skog NO Ledningsmossen, Drängedalen, Vg</t>
+          <t>N om Ledningsmossen, Drängedalen, Vg</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>343996</v>
+        <v>343920</v>
       </c>
       <c r="R49" t="n">
-        <v>6434225</v>
+        <v>6434211</v>
       </c>
       <c r="S49" t="n">
         <v>25</v>
@@ -6506,7 +6509,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>07:45</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6516,12 +6519,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>12:05</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>Rörde sig över Ledningsmossen, ropande.</t>
+          <t>07:55</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6548,10 +6546,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>118756857</v>
+        <v>118755601</v>
       </c>
       <c r="B50" t="n">
-        <v>56502</v>
+        <v>5165</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6560,46 +6558,47 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100138</v>
+        <v>102204</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Grönhjon</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Callidium aeneum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(De Geer, 1775)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr"/>
       <c r="K50" t="inlineStr"/>
       <c r="L50" t="inlineStr"/>
       <c r="M50" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Häll 3 NV Bredmossen, Drängedalen, Vg</t>
+          <t>Kjolgran N Ledningsmossen, Drängedalen, Vg</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>344067</v>
+        <v>343953</v>
       </c>
       <c r="R50" t="n">
-        <v>6434348</v>
+        <v>6434253</v>
       </c>
       <c r="S50" t="n">
         <v>25</v>
@@ -6631,7 +6630,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6641,7 +6640,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6650,6 +6649,7 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
+      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 9045-2024 artfynd.xlsx
+++ b/artfynd/A 9045-2024 artfynd.xlsx
@@ -6293,10 +6293,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>118756709</v>
+        <v>118755601</v>
       </c>
       <c r="B48" t="n">
-        <v>57148</v>
+        <v>5165</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6305,50 +6305,47 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100100</v>
+        <v>102204</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Bivråk</t>
+          <t>Grönhjon</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Pernis apivorus</t>
+          <t>Callidium aeneum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(De Geer, 1775)</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr"/>
       <c r="K48" t="inlineStr"/>
       <c r="L48" t="inlineStr"/>
       <c r="M48" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Skog NO Ledningsmossen, Drängedalen, Vg</t>
+          <t>Kjolgran N Ledningsmossen, Drängedalen, Vg</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>343996</v>
+        <v>343953</v>
       </c>
       <c r="R48" t="n">
-        <v>6434225</v>
+        <v>6434253</v>
       </c>
       <c r="S48" t="n">
         <v>25</v>
@@ -6380,7 +6377,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6390,12 +6387,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>12:05</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Rörde sig över Ledningsmossen, ropande.</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6404,6 +6396,7 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
+      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
@@ -6422,10 +6415,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>118756024</v>
+        <v>118756709</v>
       </c>
       <c r="B49" t="n">
-        <v>57443</v>
+        <v>57148</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6434,25 +6427,25 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>103021</v>
+        <v>100100</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Bivråk</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Pernis apivorus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -6464,20 +6457,20 @@
       <c r="L49" t="inlineStr"/>
       <c r="M49" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>N om Ledningsmossen, Drängedalen, Vg</t>
+          <t>Skog NO Ledningsmossen, Drängedalen, Vg</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>343920</v>
+        <v>343996</v>
       </c>
       <c r="R49" t="n">
-        <v>6434211</v>
+        <v>6434225</v>
       </c>
       <c r="S49" t="n">
         <v>25</v>
@@ -6509,7 +6502,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>07:45</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6519,7 +6512,12 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>07:55</t>
+          <t>12:05</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Rörde sig över Ledningsmossen, ropande.</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6546,10 +6544,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>118755601</v>
+        <v>118756024</v>
       </c>
       <c r="B50" t="n">
-        <v>5165</v>
+        <v>57443</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6562,43 +6560,46 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>102204</v>
+        <v>103021</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Grönhjon</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Callidium aeneum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(De Geer, 1775)</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr"/>
-      <c r="J50" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K50" t="inlineStr"/>
       <c r="L50" t="inlineStr"/>
       <c r="M50" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Kjolgran N Ledningsmossen, Drängedalen, Vg</t>
+          <t>N om Ledningsmossen, Drängedalen, Vg</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>343953</v>
+        <v>343920</v>
       </c>
       <c r="R50" t="n">
-        <v>6434253</v>
+        <v>6434211</v>
       </c>
       <c r="S50" t="n">
         <v>25</v>
@@ -6630,7 +6631,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>07:45</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6640,7 +6641,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>07:55</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6649,7 +6650,6 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
-      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 9045-2024 artfynd.xlsx
+++ b/artfynd/A 9045-2024 artfynd.xlsx
@@ -6173,10 +6173,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>118756857</v>
+        <v>118756709</v>
       </c>
       <c r="B47" t="n">
-        <v>56502</v>
+        <v>57148</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -6189,42 +6189,46 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100138</v>
+        <v>100100</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Bivråk</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Pernis apivorus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K47" t="inlineStr"/>
       <c r="L47" t="inlineStr"/>
       <c r="M47" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Häll 3 NV Bredmossen, Drängedalen, Vg</t>
+          <t>Skog NO Ledningsmossen, Drängedalen, Vg</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>344067</v>
+        <v>343996</v>
       </c>
       <c r="R47" t="n">
-        <v>6434348</v>
+        <v>6434225</v>
       </c>
       <c r="S47" t="n">
         <v>25</v>
@@ -6256,7 +6260,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -6266,7 +6270,12 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>12:05</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Rörde sig över Ledningsmossen, ropande.</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6293,10 +6302,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>118755601</v>
+        <v>118756024</v>
       </c>
       <c r="B48" t="n">
-        <v>5165</v>
+        <v>57443</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6309,43 +6318,46 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>102204</v>
+        <v>103021</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Grönhjon</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Callidium aeneum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(De Geer, 1775)</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr"/>
-      <c r="J48" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K48" t="inlineStr"/>
       <c r="L48" t="inlineStr"/>
       <c r="M48" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Kjolgran N Ledningsmossen, Drängedalen, Vg</t>
+          <t>N om Ledningsmossen, Drängedalen, Vg</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>343953</v>
+        <v>343920</v>
       </c>
       <c r="R48" t="n">
-        <v>6434253</v>
+        <v>6434211</v>
       </c>
       <c r="S48" t="n">
         <v>25</v>
@@ -6377,7 +6389,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>07:45</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6387,7 +6399,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>07:55</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6396,7 +6408,6 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
-      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
@@ -6415,10 +6426,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>118756709</v>
+        <v>118755601</v>
       </c>
       <c r="B49" t="n">
-        <v>57148</v>
+        <v>5165</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6427,50 +6438,47 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100100</v>
+        <v>102204</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Bivråk</t>
+          <t>Grönhjon</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Pernis apivorus</t>
+          <t>Callidium aeneum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(De Geer, 1775)</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr"/>
       <c r="K49" t="inlineStr"/>
       <c r="L49" t="inlineStr"/>
       <c r="M49" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Skog NO Ledningsmossen, Drängedalen, Vg</t>
+          <t>Kjolgran N Ledningsmossen, Drängedalen, Vg</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>343996</v>
+        <v>343953</v>
       </c>
       <c r="R49" t="n">
-        <v>6434225</v>
+        <v>6434253</v>
       </c>
       <c r="S49" t="n">
         <v>25</v>
@@ -6502,7 +6510,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6512,12 +6520,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>12:05</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>Rörde sig över Ledningsmossen, ropande.</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6526,6 +6529,7 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
+      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
@@ -6544,10 +6548,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>118756024</v>
+        <v>118756857</v>
       </c>
       <c r="B50" t="n">
-        <v>57443</v>
+        <v>56502</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6556,50 +6560,46 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>103021</v>
+        <v>100138</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
       <c r="K50" t="inlineStr"/>
       <c r="L50" t="inlineStr"/>
       <c r="M50" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>N om Ledningsmossen, Drängedalen, Vg</t>
+          <t>Häll 3 NV Bredmossen, Drängedalen, Vg</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>343920</v>
+        <v>344067</v>
       </c>
       <c r="R50" t="n">
-        <v>6434211</v>
+        <v>6434348</v>
       </c>
       <c r="S50" t="n">
         <v>25</v>
@@ -6631,7 +6631,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>07:45</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6641,7 +6641,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>07:55</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AD50" t="b">

--- a/artfynd/A 9045-2024 artfynd.xlsx
+++ b/artfynd/A 9045-2024 artfynd.xlsx
@@ -7301,10 +7301,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>119447676</v>
+        <v>119446914</v>
       </c>
       <c r="B56" t="n">
-        <v>94321</v>
+        <v>57463</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -7313,42 +7313,46 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>2810</v>
+        <v>103021</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
-      <c r="J56" t="inlineStr"/>
       <c r="K56" t="inlineStr"/>
       <c r="L56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Kant mot hygge NV Bredmossen, Drängedalen , Vg</t>
+          <t>Sumpskog NV Bredmossen, NO kanten, Drängedalen, Vg</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>344144</v>
+        <v>344161</v>
       </c>
       <c r="R56" t="n">
-        <v>6434438</v>
+        <v>6434293</v>
       </c>
       <c r="S56" t="n">
         <v>25</v>
@@ -7380,7 +7384,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>07:25</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -7390,12 +7394,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>12:15</t>
-        </is>
-      </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>Mycket.</t>
+          <t>07:25</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7404,7 +7403,6 @@
       <c r="AE56" t="b">
         <v>0</v>
       </c>
-      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
@@ -7423,10 +7421,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>119446914</v>
+        <v>119447676</v>
       </c>
       <c r="B57" t="n">
-        <v>57463</v>
+        <v>94321</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -7435,46 +7433,42 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>103021</v>
+        <v>2810</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
+      <c r="J57" t="inlineStr"/>
       <c r="K57" t="inlineStr"/>
       <c r="L57" t="inlineStr"/>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Sumpskog NV Bredmossen, NO kanten, Drängedalen, Vg</t>
+          <t>Kant mot hygge NV Bredmossen, Drängedalen , Vg</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>344161</v>
+        <v>344144</v>
       </c>
       <c r="R57" t="n">
-        <v>6434293</v>
+        <v>6434438</v>
       </c>
       <c r="S57" t="n">
         <v>25</v>
@@ -7506,7 +7500,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>07:25</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -7516,7 +7510,12 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>07:25</t>
+          <t>12:15</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Mycket.</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7525,6 +7524,7 @@
       <c r="AE57" t="b">
         <v>0</v>
       </c>
+      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 9045-2024 artfynd.xlsx
+++ b/artfynd/A 9045-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY59"/>
+  <dimension ref="A1:AY67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7790,6 +7790,964 @@
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>120391963</v>
+      </c>
+      <c r="B60" t="n">
+        <v>5168</v>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>102204</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Grönhjon</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Callidium aeneum</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>(De Geer, 1775)</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="J60" t="inlineStr"/>
+      <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr"/>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>Kjolgran 8 Ö Ledningsmossen, Drängedalen, Vg</t>
+        </is>
+      </c>
+      <c r="Q60" t="n">
+        <v>344145</v>
+      </c>
+      <c r="R60" t="n">
+        <v>6434343</v>
+      </c>
+      <c r="S60" t="n">
+        <v>25</v>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Hålanda</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>2024-10-06</t>
+        </is>
+      </c>
+      <c r="Z60" t="inlineStr">
+        <is>
+          <t>13:10</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>2024-10-06</t>
+        </is>
+      </c>
+      <c r="AB60" t="inlineStr">
+        <is>
+          <t>13:10</t>
+        </is>
+      </c>
+      <c r="AD60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF60" t="inlineStr"/>
+      <c r="AG60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT60" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>Ola Freijd</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>Ola Freijd</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>120408243</v>
+      </c>
+      <c r="B61" t="n">
+        <v>57336</v>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr"/>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>Bredmossen, Vg</t>
+        </is>
+      </c>
+      <c r="Q61" t="n">
+        <v>344249</v>
+      </c>
+      <c r="R61" t="n">
+        <v>6434428</v>
+      </c>
+      <c r="S61" t="n">
+        <v>5</v>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Hålanda</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>2024-05-21</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>2024-05-21</t>
+        </is>
+      </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>Ganska färska hack, vid basen av död gran.</t>
+        </is>
+      </c>
+      <c r="AD61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT61" t="inlineStr"/>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>Lars Gerre</t>
+        </is>
+      </c>
+      <c r="AX61" t="inlineStr">
+        <is>
+          <t>Lars Gerre</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>120408193</v>
+      </c>
+      <c r="B62" t="n">
+        <v>5189</v>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>105930</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Vågbandad barkbock</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Semanotus undatus</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
+      <c r="J62" t="inlineStr"/>
+      <c r="K62" t="inlineStr"/>
+      <c r="L62" t="inlineStr"/>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr"/>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>Bredmossen, Vg</t>
+        </is>
+      </c>
+      <c r="Q62" t="n">
+        <v>344249</v>
+      </c>
+      <c r="R62" t="n">
+        <v>6434428</v>
+      </c>
+      <c r="S62" t="n">
+        <v>5</v>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Hålanda</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>2024-05-21</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>2024-05-21</t>
+        </is>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>I död gran.</t>
+        </is>
+      </c>
+      <c r="AD62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF62" t="inlineStr"/>
+      <c r="AG62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT62" t="inlineStr"/>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>Lars Gerre</t>
+        </is>
+      </c>
+      <c r="AX62" t="inlineStr">
+        <is>
+          <t>Lars Gerre</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>120392393</v>
+      </c>
+      <c r="B63" t="n">
+        <v>57473</v>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="K63" t="inlineStr"/>
+      <c r="L63" t="inlineStr"/>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr"/>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>Skog 2 NV Bredmossen, Drängedalen , Vg</t>
+        </is>
+      </c>
+      <c r="Q63" t="n">
+        <v>344222</v>
+      </c>
+      <c r="R63" t="n">
+        <v>6434363</v>
+      </c>
+      <c r="S63" t="n">
+        <v>25</v>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Hålanda</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>2024-10-06</t>
+        </is>
+      </c>
+      <c r="Z63" t="inlineStr">
+        <is>
+          <t>11:55</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>2024-10-06</t>
+        </is>
+      </c>
+      <c r="AB63" t="inlineStr">
+        <is>
+          <t>11:55</t>
+        </is>
+      </c>
+      <c r="AD63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT63" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>Ola Freijd</t>
+        </is>
+      </c>
+      <c r="AX63" t="inlineStr">
+        <is>
+          <t>Ola Freijd</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>120391922</v>
+      </c>
+      <c r="B64" t="n">
+        <v>5168</v>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>102204</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Grönhjon</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Callidium aeneum</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>(De Geer, 1775)</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="J64" t="inlineStr"/>
+      <c r="K64" t="inlineStr"/>
+      <c r="L64" t="inlineStr"/>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N64" t="inlineStr"/>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>Kjolgran 7 Ö Ledningsmossen, Drängedalen, Vg</t>
+        </is>
+      </c>
+      <c r="Q64" t="n">
+        <v>344183</v>
+      </c>
+      <c r="R64" t="n">
+        <v>6434312</v>
+      </c>
+      <c r="S64" t="n">
+        <v>25</v>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>Hålanda</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>2024-10-06</t>
+        </is>
+      </c>
+      <c r="Z64" t="inlineStr">
+        <is>
+          <t>11:40</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>2024-10-06</t>
+        </is>
+      </c>
+      <c r="AB64" t="inlineStr">
+        <is>
+          <t>11:40</t>
+        </is>
+      </c>
+      <c r="AD64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF64" t="inlineStr"/>
+      <c r="AG64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT64" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>Ola Freijd</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>Ola Freijd</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>120392432</v>
+      </c>
+      <c r="B65" t="n">
+        <v>57473</v>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
+      <c r="K65" t="inlineStr"/>
+      <c r="L65" t="inlineStr"/>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N65" t="inlineStr"/>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>Skog SO Trehörningen, Drängedalen, Vg</t>
+        </is>
+      </c>
+      <c r="Q65" t="n">
+        <v>343589</v>
+      </c>
+      <c r="R65" t="n">
+        <v>6434074</v>
+      </c>
+      <c r="S65" t="n">
+        <v>25</v>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>Hålanda</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>2024-10-06</t>
+        </is>
+      </c>
+      <c r="Z65" t="inlineStr">
+        <is>
+          <t>16:40</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>2024-10-06</t>
+        </is>
+      </c>
+      <c r="AB65" t="inlineStr">
+        <is>
+          <t>16:40</t>
+        </is>
+      </c>
+      <c r="AD65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT65" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>Ola Freijd</t>
+        </is>
+      </c>
+      <c r="AX65" t="inlineStr">
+        <is>
+          <t>Ola Freijd</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>120391898</v>
+      </c>
+      <c r="B66" t="n">
+        <v>5168</v>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>102204</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Grönhjon</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Callidium aeneum</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>(De Geer, 1775)</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
+      <c r="J66" t="inlineStr"/>
+      <c r="K66" t="inlineStr"/>
+      <c r="L66" t="inlineStr"/>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N66" t="inlineStr"/>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>Kjolgran 6 Ö Ledningsmossen, Drängedalen, Vg</t>
+        </is>
+      </c>
+      <c r="Q66" t="n">
+        <v>344183</v>
+      </c>
+      <c r="R66" t="n">
+        <v>6434303</v>
+      </c>
+      <c r="S66" t="n">
+        <v>25</v>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>Hålanda</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>2024-10-06</t>
+        </is>
+      </c>
+      <c r="Z66" t="inlineStr">
+        <is>
+          <t>11:30</t>
+        </is>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>2024-10-06</t>
+        </is>
+      </c>
+      <c r="AB66" t="inlineStr">
+        <is>
+          <t>11:30</t>
+        </is>
+      </c>
+      <c r="AD66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF66" t="inlineStr"/>
+      <c r="AG66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT66" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>Ola Freijd</t>
+        </is>
+      </c>
+      <c r="AX66" t="inlineStr">
+        <is>
+          <t>Ola Freijd</t>
+        </is>
+      </c>
+      <c r="AY66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>120408289</v>
+      </c>
+      <c r="B67" t="n">
+        <v>57996</v>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>103044</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Grönsiska</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Spinus spinus</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
+      <c r="K67" t="inlineStr"/>
+      <c r="L67" t="inlineStr"/>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N67" t="inlineStr"/>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>Bredmossen, Vg</t>
+        </is>
+      </c>
+      <c r="Q67" t="n">
+        <v>344249</v>
+      </c>
+      <c r="R67" t="n">
+        <v>6434428</v>
+      </c>
+      <c r="S67" t="n">
+        <v>5</v>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>Hålanda</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr">
+        <is>
+          <t>2024-05-21</t>
+        </is>
+      </c>
+      <c r="Z67" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>2024-05-21</t>
+        </is>
+      </c>
+      <c r="AB67" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="AD67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT67" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>Lars Gerre</t>
+        </is>
+      </c>
+      <c r="AX67" t="inlineStr">
+        <is>
+          <t>Lars Gerre</t>
+        </is>
+      </c>
+      <c r="AY67" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 9045-2024 artfynd.xlsx
+++ b/artfynd/A 9045-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY67"/>
+  <dimension ref="A1:AY71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8748,6 +8748,488 @@
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>120419793</v>
+      </c>
+      <c r="B68" t="n">
+        <v>96198</v>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>2569</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Stor revmossa</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Bazzania trilobata</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>(L.) Gray</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
+      <c r="J68" t="inlineStr"/>
+      <c r="K68" t="inlineStr"/>
+      <c r="L68" t="inlineStr"/>
+      <c r="N68" t="inlineStr"/>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>Trehörningen, sydost om, Vg</t>
+        </is>
+      </c>
+      <c r="Q68" t="n">
+        <v>343605</v>
+      </c>
+      <c r="R68" t="n">
+        <v>6434107</v>
+      </c>
+      <c r="S68" t="n">
+        <v>5</v>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>Hålanda</t>
+        </is>
+      </c>
+      <c r="Y68" t="inlineStr">
+        <is>
+          <t>2024-05-21</t>
+        </is>
+      </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>2024-05-21</t>
+        </is>
+      </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>Några större tuvor.</t>
+        </is>
+      </c>
+      <c r="AD68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF68" t="inlineStr"/>
+      <c r="AG68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT68" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>Lars Gerre</t>
+        </is>
+      </c>
+      <c r="AX68" t="inlineStr">
+        <is>
+          <t>Lars Gerre</t>
+        </is>
+      </c>
+      <c r="AY68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>120419416</v>
+      </c>
+      <c r="B69" t="n">
+        <v>57473</v>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr"/>
+      <c r="L69" t="inlineStr"/>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="N69" t="inlineStr"/>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>Bredmossen, nordväst om, Vg</t>
+        </is>
+      </c>
+      <c r="Q69" t="n">
+        <v>344070</v>
+      </c>
+      <c r="R69" t="n">
+        <v>6434330</v>
+      </c>
+      <c r="S69" t="n">
+        <v>10</v>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>Hålanda</t>
+        </is>
+      </c>
+      <c r="Y69" t="inlineStr">
+        <is>
+          <t>2024-05-21</t>
+        </is>
+      </c>
+      <c r="Z69" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>2024-05-21</t>
+        </is>
+      </c>
+      <c r="AB69" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>I kanten av sumpskog.</t>
+        </is>
+      </c>
+      <c r="AD69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT69" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>Lars Gerre</t>
+        </is>
+      </c>
+      <c r="AX69" t="inlineStr">
+        <is>
+          <t>Lars Gerre</t>
+        </is>
+      </c>
+      <c r="AY69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>120419661</v>
+      </c>
+      <c r="B70" t="n">
+        <v>5189</v>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>105930</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Vågbandad barkbock</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Semanotus undatus</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
+      <c r="J70" t="inlineStr"/>
+      <c r="K70" t="inlineStr"/>
+      <c r="L70" t="inlineStr"/>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N70" t="inlineStr"/>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>Ledningsmossen, väster om, Vg</t>
+        </is>
+      </c>
+      <c r="Q70" t="n">
+        <v>343654</v>
+      </c>
+      <c r="R70" t="n">
+        <v>6434098</v>
+      </c>
+      <c r="S70" t="n">
+        <v>5</v>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>Hålanda</t>
+        </is>
+      </c>
+      <c r="Y70" t="inlineStr">
+        <is>
+          <t>2024-05-21</t>
+        </is>
+      </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>2024-05-21</t>
+        </is>
+      </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>I död gran,</t>
+        </is>
+      </c>
+      <c r="AD70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF70" t="inlineStr"/>
+      <c r="AG70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT70" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>Lars Gerre</t>
+        </is>
+      </c>
+      <c r="AX70" t="inlineStr">
+        <is>
+          <t>Lars Gerre</t>
+        </is>
+      </c>
+      <c r="AY70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>120419699</v>
+      </c>
+      <c r="B71" t="n">
+        <v>57689</v>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr"/>
+      <c r="L71" t="inlineStr"/>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N71" t="inlineStr"/>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>Ledningsmossen, väster om, Vg</t>
+        </is>
+      </c>
+      <c r="Q71" t="n">
+        <v>343654</v>
+      </c>
+      <c r="R71" t="n">
+        <v>6434098</v>
+      </c>
+      <c r="S71" t="n">
+        <v>5</v>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t>Hålanda</t>
+        </is>
+      </c>
+      <c r="Y71" t="inlineStr">
+        <is>
+          <t>2024-05-21</t>
+        </is>
+      </c>
+      <c r="Z71" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>2024-05-21</t>
+        </is>
+      </c>
+      <c r="AB71" t="inlineStr">
+        <is>
+          <t>18:30</t>
+        </is>
+      </c>
+      <c r="AD71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT71" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>Lars Gerre</t>
+        </is>
+      </c>
+      <c r="AX71" t="inlineStr">
+        <is>
+          <t>Lars Gerre</t>
+        </is>
+      </c>
+      <c r="AY71" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 9045-2024 artfynd.xlsx
+++ b/artfynd/A 9045-2024 artfynd.xlsx
@@ -7792,7 +7792,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>120391963</v>
+        <v>120391922</v>
       </c>
       <c r="B60" t="n">
         <v>5168</v>
@@ -7837,14 +7837,14 @@
       <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Kjolgran 8 Ö Ledningsmossen, Drängedalen, Vg</t>
+          <t>Kjolgran 7 Ö Ledningsmossen, Drängedalen, Vg</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>344145</v>
+        <v>344183</v>
       </c>
       <c r="R60" t="n">
-        <v>6434343</v>
+        <v>6434312</v>
       </c>
       <c r="S60" t="n">
         <v>25</v>
@@ -7876,7 +7876,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7886,7 +7886,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7914,10 +7914,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>120408243</v>
+        <v>120392393</v>
       </c>
       <c r="B61" t="n">
-        <v>57336</v>
+        <v>57473</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7930,21 +7930,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7952,23 +7952,23 @@
       <c r="L61" t="inlineStr"/>
       <c r="M61" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Bredmossen, Vg</t>
+          <t>Skog 2 NV Bredmossen, Drängedalen , Vg</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>344249</v>
+        <v>344222</v>
       </c>
       <c r="R61" t="n">
-        <v>6434428</v>
+        <v>6434363</v>
       </c>
       <c r="S61" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7992,17 +7992,22 @@
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>2024-05-21</t>
+          <t>2024-10-06</t>
+        </is>
+      </c>
+      <c r="Z61" t="inlineStr">
+        <is>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2024-05-21</t>
-        </is>
-      </c>
-      <c r="AC61" t="inlineStr">
-        <is>
-          <t>Ganska färska hack, vid basen av död gran.</t>
+          <t>2024-10-06</t>
+        </is>
+      </c>
+      <c r="AB61" t="inlineStr">
+        <is>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -8017,12 +8022,12 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Lars Gerre</t>
+          <t>Ola Freijd</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Lars Gerre</t>
+          <t>Ola Freijd</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
@@ -8146,10 +8151,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>120392393</v>
+        <v>120391963</v>
       </c>
       <c r="B63" t="n">
-        <v>57473</v>
+        <v>5168</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -8162,42 +8167,43 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>103021</v>
+        <v>102204</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Grönhjon</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Callidium aeneum</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(De Geer, 1775)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
+      <c r="J63" t="inlineStr"/>
       <c r="K63" t="inlineStr"/>
       <c r="L63" t="inlineStr"/>
       <c r="M63" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Skog 2 NV Bredmossen, Drängedalen , Vg</t>
+          <t>Kjolgran 8 Ö Ledningsmossen, Drängedalen, Vg</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>344222</v>
+        <v>344145</v>
       </c>
       <c r="R63" t="n">
-        <v>6434363</v>
+        <v>6434343</v>
       </c>
       <c r="S63" t="n">
         <v>25</v>
@@ -8229,7 +8235,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -8239,7 +8245,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -8248,6 +8254,7 @@
       <c r="AE63" t="b">
         <v>0</v>
       </c>
+      <c r="AF63" t="inlineStr"/>
       <c r="AG63" t="b">
         <v>0</v>
       </c>
@@ -8266,7 +8273,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>120391922</v>
+        <v>120391898</v>
       </c>
       <c r="B64" t="n">
         <v>5168</v>
@@ -8311,14 +8318,14 @@
       <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Kjolgran 7 Ö Ledningsmossen, Drängedalen, Vg</t>
+          <t>Kjolgran 6 Ö Ledningsmossen, Drängedalen, Vg</t>
         </is>
       </c>
       <c r="Q64" t="n">
         <v>344183</v>
       </c>
       <c r="R64" t="n">
-        <v>6434312</v>
+        <v>6434303</v>
       </c>
       <c r="S64" t="n">
         <v>25</v>
@@ -8350,7 +8357,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -8360,7 +8367,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -8388,10 +8395,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>120392432</v>
+        <v>120408243</v>
       </c>
       <c r="B65" t="n">
-        <v>57473</v>
+        <v>57336</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -8404,21 +8411,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -8426,23 +8433,23 @@
       <c r="L65" t="inlineStr"/>
       <c r="M65" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Skog SO Trehörningen, Drängedalen, Vg</t>
+          <t>Bredmossen, Vg</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>343589</v>
+        <v>344249</v>
       </c>
       <c r="R65" t="n">
-        <v>6434074</v>
+        <v>6434428</v>
       </c>
       <c r="S65" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -8466,22 +8473,17 @@
       </c>
       <c r="Y65" t="inlineStr">
         <is>
-          <t>2024-10-06</t>
-        </is>
-      </c>
-      <c r="Z65" t="inlineStr">
-        <is>
-          <t>16:40</t>
+          <t>2024-05-21</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>2024-10-06</t>
-        </is>
-      </c>
-      <c r="AB65" t="inlineStr">
-        <is>
-          <t>16:40</t>
+          <t>2024-05-21</t>
+        </is>
+      </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>Ganska färska hack, vid basen av död gran.</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -8496,22 +8498,22 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Ola Freijd</t>
+          <t>Lars Gerre</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Ola Freijd</t>
+          <t>Lars Gerre</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>120391898</v>
+        <v>120408289</v>
       </c>
       <c r="B66" t="n">
-        <v>5168</v>
+        <v>57996</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -8520,50 +8522,49 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>102204</v>
+        <v>103044</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Grönhjon</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Callidium aeneum</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(De Geer, 1775)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
-      <c r="J66" t="inlineStr"/>
       <c r="K66" t="inlineStr"/>
       <c r="L66" t="inlineStr"/>
       <c r="M66" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Kjolgran 6 Ö Ledningsmossen, Drängedalen, Vg</t>
+          <t>Bredmossen, Vg</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>344183</v>
+        <v>344249</v>
       </c>
       <c r="R66" t="n">
-        <v>6434303</v>
+        <v>6434428</v>
       </c>
       <c r="S66" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -8587,22 +8588,22 @@
       </c>
       <c r="Y66" t="inlineStr">
         <is>
-          <t>2024-10-06</t>
+          <t>2024-05-21</t>
         </is>
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>2024-10-06</t>
+          <t>2024-05-21</t>
         </is>
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8611,29 +8612,28 @@
       <c r="AE66" t="b">
         <v>0</v>
       </c>
-      <c r="AF66" t="inlineStr"/>
       <c r="AG66" t="b">
         <v>0</v>
       </c>
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Ola Freijd</t>
+          <t>Lars Gerre</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Ola Freijd</t>
+          <t>Lars Gerre</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>120408289</v>
+        <v>120392432</v>
       </c>
       <c r="B67" t="n">
-        <v>57996</v>
+        <v>57473</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -8642,25 +8642,25 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>103044</v>
+        <v>103021</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -8674,17 +8674,17 @@
       <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Bredmossen, Vg</t>
+          <t>Skog SO Trehörningen, Drängedalen, Vg</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>344249</v>
+        <v>343589</v>
       </c>
       <c r="R67" t="n">
-        <v>6434428</v>
+        <v>6434074</v>
       </c>
       <c r="S67" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -8708,22 +8708,22 @@
       </c>
       <c r="Y67" t="inlineStr">
         <is>
-          <t>2024-05-21</t>
+          <t>2024-10-06</t>
         </is>
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>2024-05-21</t>
+          <t>2024-10-06</t>
         </is>
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8738,12 +8738,12 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Lars Gerre</t>
+          <t>Ola Freijd</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Lars Gerre</t>
+          <t>Ola Freijd</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
@@ -8991,10 +8991,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>120419661</v>
+        <v>120419699</v>
       </c>
       <c r="B70" t="n">
-        <v>5189</v>
+        <v>57689</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -9007,16 +9007,16 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>105930</v>
+        <v>103015</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -9024,13 +9024,16 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I70" t="inlineStr"/>
-      <c r="J70" t="inlineStr"/>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K70" t="inlineStr"/>
       <c r="L70" t="inlineStr"/>
       <c r="M70" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N70" t="inlineStr"/>
@@ -9073,14 +9076,19 @@
           <t>2024-05-21</t>
         </is>
       </c>
+      <c r="Z70" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
       <c r="AA70" t="inlineStr">
         <is>
           <t>2024-05-21</t>
         </is>
       </c>
-      <c r="AC70" t="inlineStr">
-        <is>
-          <t>I död gran,</t>
+      <c r="AB70" t="inlineStr">
+        <is>
+          <t>18:30</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -9089,7 +9097,6 @@
       <c r="AE70" t="b">
         <v>0</v>
       </c>
-      <c r="AF70" t="inlineStr"/>
       <c r="AG70" t="b">
         <v>0</v>
       </c>
@@ -9108,10 +9115,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>120419699</v>
+        <v>120419661</v>
       </c>
       <c r="B71" t="n">
-        <v>57689</v>
+        <v>5189</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -9124,16 +9131,16 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>103015</v>
+        <v>105930</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -9141,16 +9148,13 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I71" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I71" t="inlineStr"/>
+      <c r="J71" t="inlineStr"/>
       <c r="K71" t="inlineStr"/>
       <c r="L71" t="inlineStr"/>
       <c r="M71" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N71" t="inlineStr"/>
@@ -9193,19 +9197,14 @@
           <t>2024-05-21</t>
         </is>
       </c>
-      <c r="Z71" t="inlineStr">
-        <is>
-          <t>18:00</t>
-        </is>
-      </c>
       <c r="AA71" t="inlineStr">
         <is>
           <t>2024-05-21</t>
         </is>
       </c>
-      <c r="AB71" t="inlineStr">
-        <is>
-          <t>18:30</t>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>I död gran,</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -9214,6 +9213,7 @@
       <c r="AE71" t="b">
         <v>0</v>
       </c>
+      <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 9045-2024 artfynd.xlsx
+++ b/artfynd/A 9045-2024 artfynd.xlsx
@@ -7914,7 +7914,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>120392393</v>
+        <v>120392432</v>
       </c>
       <c r="B61" t="n">
         <v>57473</v>
@@ -7958,14 +7958,14 @@
       <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Skog 2 NV Bredmossen, Drängedalen , Vg</t>
+          <t>Skog SO Trehörningen, Drängedalen, Vg</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>344222</v>
+        <v>343589</v>
       </c>
       <c r="R61" t="n">
-        <v>6434363</v>
+        <v>6434074</v>
       </c>
       <c r="S61" t="n">
         <v>25</v>
@@ -7997,7 +7997,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -8007,7 +8007,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -8034,10 +8034,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>120408193</v>
+        <v>120392393</v>
       </c>
       <c r="B62" t="n">
-        <v>5189</v>
+        <v>57473</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -8046,50 +8046,49 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>105930</v>
+        <v>103021</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
-      <c r="J62" t="inlineStr"/>
       <c r="K62" t="inlineStr"/>
       <c r="L62" t="inlineStr"/>
       <c r="M62" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Bredmossen, Vg</t>
+          <t>Skog 2 NV Bredmossen, Drängedalen , Vg</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>344249</v>
+        <v>344222</v>
       </c>
       <c r="R62" t="n">
-        <v>6434428</v>
+        <v>6434363</v>
       </c>
       <c r="S62" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -8113,17 +8112,22 @@
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>2024-05-21</t>
+          <t>2024-10-06</t>
+        </is>
+      </c>
+      <c r="Z62" t="inlineStr">
+        <is>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2024-05-21</t>
-        </is>
-      </c>
-      <c r="AC62" t="inlineStr">
-        <is>
-          <t>I död gran.</t>
+          <t>2024-10-06</t>
+        </is>
+      </c>
+      <c r="AB62" t="inlineStr">
+        <is>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -8132,29 +8136,28 @@
       <c r="AE62" t="b">
         <v>0</v>
       </c>
-      <c r="AF62" t="inlineStr"/>
       <c r="AG62" t="b">
         <v>0</v>
       </c>
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Lars Gerre</t>
+          <t>Ola Freijd</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Lars Gerre</t>
+          <t>Ola Freijd</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>120391963</v>
+        <v>120408289</v>
       </c>
       <c r="B63" t="n">
-        <v>5168</v>
+        <v>57996</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -8163,50 +8166,49 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>102204</v>
+        <v>103044</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Grönhjon</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Callidium aeneum</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(De Geer, 1775)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
-      <c r="J63" t="inlineStr"/>
       <c r="K63" t="inlineStr"/>
       <c r="L63" t="inlineStr"/>
       <c r="M63" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Kjolgran 8 Ö Ledningsmossen, Drängedalen, Vg</t>
+          <t>Bredmossen, Vg</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>344145</v>
+        <v>344249</v>
       </c>
       <c r="R63" t="n">
-        <v>6434343</v>
+        <v>6434428</v>
       </c>
       <c r="S63" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -8230,22 +8232,22 @@
       </c>
       <c r="Y63" t="inlineStr">
         <is>
-          <t>2024-10-06</t>
+          <t>2024-05-21</t>
         </is>
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>2024-10-06</t>
+          <t>2024-05-21</t>
         </is>
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -8254,29 +8256,28 @@
       <c r="AE63" t="b">
         <v>0</v>
       </c>
-      <c r="AF63" t="inlineStr"/>
       <c r="AG63" t="b">
         <v>0</v>
       </c>
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Ola Freijd</t>
+          <t>Lars Gerre</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Ola Freijd</t>
+          <t>Lars Gerre</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>120391898</v>
+        <v>120408193</v>
       </c>
       <c r="B64" t="n">
-        <v>5168</v>
+        <v>5189</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -8285,25 +8286,25 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>102204</v>
+        <v>105930</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Grönhjon</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Callidium aeneum</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(De Geer, 1775)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -8312,23 +8313,23 @@
       <c r="L64" t="inlineStr"/>
       <c r="M64" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Kjolgran 6 Ö Ledningsmossen, Drängedalen, Vg</t>
+          <t>Bredmossen, Vg</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>344183</v>
+        <v>344249</v>
       </c>
       <c r="R64" t="n">
-        <v>6434303</v>
+        <v>6434428</v>
       </c>
       <c r="S64" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -8352,22 +8353,17 @@
       </c>
       <c r="Y64" t="inlineStr">
         <is>
-          <t>2024-10-06</t>
-        </is>
-      </c>
-      <c r="Z64" t="inlineStr">
-        <is>
-          <t>11:30</t>
+          <t>2024-05-21</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>2024-10-06</t>
-        </is>
-      </c>
-      <c r="AB64" t="inlineStr">
-        <is>
-          <t>11:30</t>
+          <t>2024-05-21</t>
+        </is>
+      </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>I död gran.</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -8383,22 +8379,22 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Ola Freijd</t>
+          <t>Lars Gerre</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Ola Freijd</t>
+          <t>Lars Gerre</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>120408243</v>
+        <v>120391963</v>
       </c>
       <c r="B65" t="n">
-        <v>57336</v>
+        <v>5168</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -8411,45 +8407,46 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>100049</v>
+        <v>102204</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grönhjon</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Callidium aeneum</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(De Geer, 1775)</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
+      <c r="J65" t="inlineStr"/>
       <c r="K65" t="inlineStr"/>
       <c r="L65" t="inlineStr"/>
       <c r="M65" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Bredmossen, Vg</t>
+          <t>Kjolgran 8 Ö Ledningsmossen, Drängedalen, Vg</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>344249</v>
+        <v>344145</v>
       </c>
       <c r="R65" t="n">
-        <v>6434428</v>
+        <v>6434343</v>
       </c>
       <c r="S65" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -8473,17 +8470,22 @@
       </c>
       <c r="Y65" t="inlineStr">
         <is>
-          <t>2024-05-21</t>
+          <t>2024-10-06</t>
+        </is>
+      </c>
+      <c r="Z65" t="inlineStr">
+        <is>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>2024-05-21</t>
-        </is>
-      </c>
-      <c r="AC65" t="inlineStr">
-        <is>
-          <t>Ganska färska hack, vid basen av död gran.</t>
+          <t>2024-10-06</t>
+        </is>
+      </c>
+      <c r="AB65" t="inlineStr">
+        <is>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -8492,28 +8494,29 @@
       <c r="AE65" t="b">
         <v>0</v>
       </c>
+      <c r="AF65" t="inlineStr"/>
       <c r="AG65" t="b">
         <v>0</v>
       </c>
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Lars Gerre</t>
+          <t>Ola Freijd</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Lars Gerre</t>
+          <t>Ola Freijd</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>120408289</v>
+        <v>120408243</v>
       </c>
       <c r="B66" t="n">
-        <v>57996</v>
+        <v>57336</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -8522,20 +8525,20 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>103044</v>
+        <v>100049</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -8548,7 +8551,7 @@
       <c r="L66" t="inlineStr"/>
       <c r="M66" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N66" t="inlineStr"/>
@@ -8591,19 +8594,14 @@
           <t>2024-05-21</t>
         </is>
       </c>
-      <c r="Z66" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
       <c r="AA66" t="inlineStr">
         <is>
           <t>2024-05-21</t>
         </is>
       </c>
-      <c r="AB66" t="inlineStr">
-        <is>
-          <t>18:00</t>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>Ganska färska hack, vid basen av död gran.</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8630,10 +8628,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>120392432</v>
+        <v>120391898</v>
       </c>
       <c r="B67" t="n">
-        <v>57473</v>
+        <v>5168</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -8646,42 +8644,43 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>103021</v>
+        <v>102204</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Grönhjon</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Callidium aeneum</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(De Geer, 1775)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
+      <c r="J67" t="inlineStr"/>
       <c r="K67" t="inlineStr"/>
       <c r="L67" t="inlineStr"/>
       <c r="M67" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Skog SO Trehörningen, Drängedalen, Vg</t>
+          <t>Kjolgran 6 Ö Ledningsmossen, Drängedalen, Vg</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>343589</v>
+        <v>344183</v>
       </c>
       <c r="R67" t="n">
-        <v>6434074</v>
+        <v>6434303</v>
       </c>
       <c r="S67" t="n">
         <v>25</v>
@@ -8713,7 +8712,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -8723,7 +8722,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8732,6 +8731,7 @@
       <c r="AE67" t="b">
         <v>0</v>
       </c>
+      <c r="AF67" t="inlineStr"/>
       <c r="AG67" t="b">
         <v>0</v>
       </c>
@@ -8750,10 +8750,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>120419793</v>
+        <v>120419416</v>
       </c>
       <c r="B68" t="n">
-        <v>96198</v>
+        <v>57473</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -8762,45 +8762,53 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>2569</v>
+        <v>103021</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr"/>
-      <c r="J68" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K68" t="inlineStr"/>
       <c r="L68" t="inlineStr"/>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
       <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Trehörningen, sydost om, Vg</t>
+          <t>Bredmossen, nordväst om, Vg</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>343605</v>
+        <v>344070</v>
       </c>
       <c r="R68" t="n">
-        <v>6434107</v>
+        <v>6434330</v>
       </c>
       <c r="S68" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -8827,14 +8835,24 @@
           <t>2024-05-21</t>
         </is>
       </c>
+      <c r="Z68" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
       <c r="AA68" t="inlineStr">
         <is>
           <t>2024-05-21</t>
         </is>
       </c>
+      <c r="AB68" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
       <c r="AC68" t="inlineStr">
         <is>
-          <t>Några större tuvor.</t>
+          <t>I kanten av sumpskog.</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8843,7 +8861,6 @@
       <c r="AE68" t="b">
         <v>0</v>
       </c>
-      <c r="AF68" t="inlineStr"/>
       <c r="AG68" t="b">
         <v>0</v>
       </c>
@@ -8862,10 +8879,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>120419416</v>
+        <v>120419699</v>
       </c>
       <c r="B69" t="n">
-        <v>57473</v>
+        <v>57689</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8874,25 +8891,25 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>103021</v>
+        <v>103015</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -8904,23 +8921,23 @@
       <c r="L69" t="inlineStr"/>
       <c r="M69" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Bredmossen, nordväst om, Vg</t>
+          <t>Ledningsmossen, väster om, Vg</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>344070</v>
+        <v>343654</v>
       </c>
       <c r="R69" t="n">
-        <v>6434330</v>
+        <v>6434098</v>
       </c>
       <c r="S69" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -8949,7 +8966,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8959,12 +8976,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>18:00</t>
-        </is>
-      </c>
-      <c r="AC69" t="inlineStr">
-        <is>
-          <t>I kanten av sumpskog.</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8991,10 +9003,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>120419699</v>
+        <v>120419661</v>
       </c>
       <c r="B70" t="n">
-        <v>57689</v>
+        <v>5189</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -9007,16 +9019,16 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>103015</v>
+        <v>105930</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -9024,16 +9036,13 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I70" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I70" t="inlineStr"/>
+      <c r="J70" t="inlineStr"/>
       <c r="K70" t="inlineStr"/>
       <c r="L70" t="inlineStr"/>
       <c r="M70" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N70" t="inlineStr"/>
@@ -9076,19 +9085,14 @@
           <t>2024-05-21</t>
         </is>
       </c>
-      <c r="Z70" t="inlineStr">
-        <is>
-          <t>18:00</t>
-        </is>
-      </c>
       <c r="AA70" t="inlineStr">
         <is>
           <t>2024-05-21</t>
         </is>
       </c>
-      <c r="AB70" t="inlineStr">
-        <is>
-          <t>18:30</t>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>I död gran,</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -9097,6 +9101,7 @@
       <c r="AE70" t="b">
         <v>0</v>
       </c>
+      <c r="AF70" t="inlineStr"/>
       <c r="AG70" t="b">
         <v>0</v>
       </c>
@@ -9115,10 +9120,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>120419661</v>
+        <v>120419793</v>
       </c>
       <c r="B71" t="n">
-        <v>5189</v>
+        <v>96198</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -9131,43 +9136,38 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>105930</v>
+        <v>2569</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
       <c r="J71" t="inlineStr"/>
       <c r="K71" t="inlineStr"/>
       <c r="L71" t="inlineStr"/>
-      <c r="M71" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Ledningsmossen, väster om, Vg</t>
+          <t>Trehörningen, sydost om, Vg</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>343654</v>
+        <v>343605</v>
       </c>
       <c r="R71" t="n">
-        <v>6434098</v>
+        <v>6434107</v>
       </c>
       <c r="S71" t="n">
         <v>5</v>
@@ -9204,7 +9204,7 @@
       </c>
       <c r="AC71" t="inlineStr">
         <is>
-          <t>I död gran,</t>
+          <t>Några större tuvor.</t>
         </is>
       </c>
       <c r="AD71" t="b">

--- a/artfynd/A 9045-2024 artfynd.xlsx
+++ b/artfynd/A 9045-2024 artfynd.xlsx
@@ -7792,7 +7792,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>120391922</v>
+        <v>120391898</v>
       </c>
       <c r="B60" t="n">
         <v>5168</v>
@@ -7837,14 +7837,14 @@
       <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Kjolgran 7 Ö Ledningsmossen, Drängedalen, Vg</t>
+          <t>Kjolgran 6 Ö Ledningsmossen, Drängedalen, Vg</t>
         </is>
       </c>
       <c r="Q60" t="n">
         <v>344183</v>
       </c>
       <c r="R60" t="n">
-        <v>6434312</v>
+        <v>6434303</v>
       </c>
       <c r="S60" t="n">
         <v>25</v>
@@ -7876,7 +7876,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7886,7 +7886,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7914,10 +7914,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>120392432</v>
+        <v>120408193</v>
       </c>
       <c r="B61" t="n">
-        <v>57473</v>
+        <v>5189</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7926,49 +7926,50 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>103021</v>
+        <v>105930</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
+      <c r="J61" t="inlineStr"/>
       <c r="K61" t="inlineStr"/>
       <c r="L61" t="inlineStr"/>
       <c r="M61" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Skog SO Trehörningen, Drängedalen, Vg</t>
+          <t>Bredmossen, Vg</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>343589</v>
+        <v>344249</v>
       </c>
       <c r="R61" t="n">
-        <v>6434074</v>
+        <v>6434428</v>
       </c>
       <c r="S61" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7992,22 +7993,17 @@
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>2024-10-06</t>
-        </is>
-      </c>
-      <c r="Z61" t="inlineStr">
-        <is>
-          <t>16:40</t>
+          <t>2024-05-21</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2024-10-06</t>
-        </is>
-      </c>
-      <c r="AB61" t="inlineStr">
-        <is>
-          <t>16:40</t>
+          <t>2024-05-21</t>
+        </is>
+      </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>I död gran.</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -8016,18 +8012,19 @@
       <c r="AE61" t="b">
         <v>0</v>
       </c>
+      <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="b">
         <v>0</v>
       </c>
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Ola Freijd</t>
+          <t>Lars Gerre</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Ola Freijd</t>
+          <t>Lars Gerre</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
@@ -8154,10 +8151,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>120408289</v>
+        <v>120392432</v>
       </c>
       <c r="B63" t="n">
-        <v>57996</v>
+        <v>57473</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -8166,25 +8163,25 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>103044</v>
+        <v>103021</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -8198,17 +8195,17 @@
       <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Bredmossen, Vg</t>
+          <t>Skog SO Trehörningen, Drängedalen, Vg</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>344249</v>
+        <v>343589</v>
       </c>
       <c r="R63" t="n">
-        <v>6434428</v>
+        <v>6434074</v>
       </c>
       <c r="S63" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -8232,22 +8229,22 @@
       </c>
       <c r="Y63" t="inlineStr">
         <is>
-          <t>2024-05-21</t>
+          <t>2024-10-06</t>
         </is>
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>2024-05-21</t>
+          <t>2024-10-06</t>
         </is>
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -8262,22 +8259,22 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Lars Gerre</t>
+          <t>Ola Freijd</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Lars Gerre</t>
+          <t>Ola Freijd</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>120408193</v>
+        <v>120391963</v>
       </c>
       <c r="B64" t="n">
-        <v>5189</v>
+        <v>5168</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -8286,25 +8283,25 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>105930</v>
+        <v>102204</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Grönhjon</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Callidium aeneum</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(De Geer, 1775)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -8313,23 +8310,23 @@
       <c r="L64" t="inlineStr"/>
       <c r="M64" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Bredmossen, Vg</t>
+          <t>Kjolgran 8 Ö Ledningsmossen, Drängedalen, Vg</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>344249</v>
+        <v>344145</v>
       </c>
       <c r="R64" t="n">
-        <v>6434428</v>
+        <v>6434343</v>
       </c>
       <c r="S64" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -8353,17 +8350,22 @@
       </c>
       <c r="Y64" t="inlineStr">
         <is>
-          <t>2024-05-21</t>
+          <t>2024-10-06</t>
+        </is>
+      </c>
+      <c r="Z64" t="inlineStr">
+        <is>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>2024-05-21</t>
-        </is>
-      </c>
-      <c r="AC64" t="inlineStr">
-        <is>
-          <t>I död gran.</t>
+          <t>2024-10-06</t>
+        </is>
+      </c>
+      <c r="AB64" t="inlineStr">
+        <is>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -8379,22 +8381,22 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Lars Gerre</t>
+          <t>Ola Freijd</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Lars Gerre</t>
+          <t>Ola Freijd</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>120391963</v>
+        <v>120408289</v>
       </c>
       <c r="B65" t="n">
-        <v>5168</v>
+        <v>57996</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -8403,50 +8405,49 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>102204</v>
+        <v>103044</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Grönhjon</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Callidium aeneum</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(De Geer, 1775)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
-      <c r="J65" t="inlineStr"/>
       <c r="K65" t="inlineStr"/>
       <c r="L65" t="inlineStr"/>
       <c r="M65" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Kjolgran 8 Ö Ledningsmossen, Drängedalen, Vg</t>
+          <t>Bredmossen, Vg</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>344145</v>
+        <v>344249</v>
       </c>
       <c r="R65" t="n">
-        <v>6434343</v>
+        <v>6434428</v>
       </c>
       <c r="S65" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -8470,22 +8471,22 @@
       </c>
       <c r="Y65" t="inlineStr">
         <is>
-          <t>2024-10-06</t>
+          <t>2024-05-21</t>
         </is>
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>2024-10-06</t>
+          <t>2024-05-21</t>
         </is>
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -8494,19 +8495,18 @@
       <c r="AE65" t="b">
         <v>0</v>
       </c>
-      <c r="AF65" t="inlineStr"/>
       <c r="AG65" t="b">
         <v>0</v>
       </c>
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Ola Freijd</t>
+          <t>Lars Gerre</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Ola Freijd</t>
+          <t>Lars Gerre</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
@@ -8628,7 +8628,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>120391898</v>
+        <v>120391922</v>
       </c>
       <c r="B67" t="n">
         <v>5168</v>
@@ -8673,14 +8673,14 @@
       <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Kjolgran 6 Ö Ledningsmossen, Drängedalen, Vg</t>
+          <t>Kjolgran 7 Ö Ledningsmossen, Drängedalen, Vg</t>
         </is>
       </c>
       <c r="Q67" t="n">
         <v>344183</v>
       </c>
       <c r="R67" t="n">
-        <v>6434303</v>
+        <v>6434312</v>
       </c>
       <c r="S67" t="n">
         <v>25</v>
@@ -8712,7 +8712,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -8722,7 +8722,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8750,10 +8750,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>120419416</v>
+        <v>120419793</v>
       </c>
       <c r="B68" t="n">
-        <v>57473</v>
+        <v>96198</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -8762,53 +8762,45 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>103021</v>
+        <v>2569</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) Gray</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
+      <c r="J68" t="inlineStr"/>
       <c r="K68" t="inlineStr"/>
       <c r="L68" t="inlineStr"/>
-      <c r="M68" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
       <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Bredmossen, nordväst om, Vg</t>
+          <t>Trehörningen, sydost om, Vg</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>344070</v>
+        <v>343605</v>
       </c>
       <c r="R68" t="n">
-        <v>6434330</v>
+        <v>6434107</v>
       </c>
       <c r="S68" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -8835,24 +8827,14 @@
           <t>2024-05-21</t>
         </is>
       </c>
-      <c r="Z68" t="inlineStr">
-        <is>
-          <t>17:30</t>
-        </is>
-      </c>
       <c r="AA68" t="inlineStr">
         <is>
           <t>2024-05-21</t>
         </is>
       </c>
-      <c r="AB68" t="inlineStr">
-        <is>
-          <t>18:00</t>
-        </is>
-      </c>
       <c r="AC68" t="inlineStr">
         <is>
-          <t>I kanten av sumpskog.</t>
+          <t>Några större tuvor.</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8861,6 +8843,7 @@
       <c r="AE68" t="b">
         <v>0</v>
       </c>
+      <c r="AF68" t="inlineStr"/>
       <c r="AG68" t="b">
         <v>0</v>
       </c>
@@ -8879,10 +8862,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>120419699</v>
+        <v>120419661</v>
       </c>
       <c r="B69" t="n">
-        <v>57689</v>
+        <v>5189</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8895,16 +8878,16 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>103015</v>
+        <v>105930</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -8912,16 +8895,13 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I69" t="inlineStr"/>
+      <c r="J69" t="inlineStr"/>
       <c r="K69" t="inlineStr"/>
       <c r="L69" t="inlineStr"/>
       <c r="M69" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N69" t="inlineStr"/>
@@ -8964,19 +8944,14 @@
           <t>2024-05-21</t>
         </is>
       </c>
-      <c r="Z69" t="inlineStr">
-        <is>
-          <t>18:00</t>
-        </is>
-      </c>
       <c r="AA69" t="inlineStr">
         <is>
           <t>2024-05-21</t>
         </is>
       </c>
-      <c r="AB69" t="inlineStr">
-        <is>
-          <t>18:30</t>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>I död gran,</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8985,6 +8960,7 @@
       <c r="AE69" t="b">
         <v>0</v>
       </c>
+      <c r="AF69" t="inlineStr"/>
       <c r="AG69" t="b">
         <v>0</v>
       </c>
@@ -9003,10 +8979,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>120419661</v>
+        <v>120419699</v>
       </c>
       <c r="B70" t="n">
-        <v>5189</v>
+        <v>57689</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -9019,16 +8995,16 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>105930</v>
+        <v>103015</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -9036,13 +9012,16 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I70" t="inlineStr"/>
-      <c r="J70" t="inlineStr"/>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K70" t="inlineStr"/>
       <c r="L70" t="inlineStr"/>
       <c r="M70" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N70" t="inlineStr"/>
@@ -9085,14 +9064,19 @@
           <t>2024-05-21</t>
         </is>
       </c>
+      <c r="Z70" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
       <c r="AA70" t="inlineStr">
         <is>
           <t>2024-05-21</t>
         </is>
       </c>
-      <c r="AC70" t="inlineStr">
-        <is>
-          <t>I död gran,</t>
+      <c r="AB70" t="inlineStr">
+        <is>
+          <t>18:30</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -9101,7 +9085,6 @@
       <c r="AE70" t="b">
         <v>0</v>
       </c>
-      <c r="AF70" t="inlineStr"/>
       <c r="AG70" t="b">
         <v>0</v>
       </c>
@@ -9120,10 +9103,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>120419793</v>
+        <v>120419416</v>
       </c>
       <c r="B71" t="n">
-        <v>96198</v>
+        <v>57473</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -9132,45 +9115,53 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>2569</v>
+        <v>103021</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr"/>
-      <c r="J71" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K71" t="inlineStr"/>
       <c r="L71" t="inlineStr"/>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
       <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Trehörningen, sydost om, Vg</t>
+          <t>Bredmossen, nordväst om, Vg</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>343605</v>
+        <v>344070</v>
       </c>
       <c r="R71" t="n">
-        <v>6434107</v>
+        <v>6434330</v>
       </c>
       <c r="S71" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -9197,14 +9188,24 @@
           <t>2024-05-21</t>
         </is>
       </c>
+      <c r="Z71" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
       <c r="AA71" t="inlineStr">
         <is>
           <t>2024-05-21</t>
         </is>
       </c>
+      <c r="AB71" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
       <c r="AC71" t="inlineStr">
         <is>
-          <t>Några större tuvor.</t>
+          <t>I kanten av sumpskog.</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -9213,7 +9214,6 @@
       <c r="AE71" t="b">
         <v>0</v>
       </c>
-      <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 9045-2024 artfynd.xlsx
+++ b/artfynd/A 9045-2024 artfynd.xlsx
@@ -7792,10 +7792,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>120391898</v>
+        <v>120408193</v>
       </c>
       <c r="B60" t="n">
-        <v>5168</v>
+        <v>5189</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7804,25 +7804,25 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>102204</v>
+        <v>105930</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Grönhjon</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Callidium aeneum</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(De Geer, 1775)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -7831,23 +7831,23 @@
       <c r="L60" t="inlineStr"/>
       <c r="M60" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Kjolgran 6 Ö Ledningsmossen, Drängedalen, Vg</t>
+          <t>Bredmossen, Vg</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>344183</v>
+        <v>344249</v>
       </c>
       <c r="R60" t="n">
-        <v>6434303</v>
+        <v>6434428</v>
       </c>
       <c r="S60" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7871,22 +7871,17 @@
       </c>
       <c r="Y60" t="inlineStr">
         <is>
-          <t>2024-10-06</t>
-        </is>
-      </c>
-      <c r="Z60" t="inlineStr">
-        <is>
-          <t>11:30</t>
+          <t>2024-05-21</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>2024-10-06</t>
-        </is>
-      </c>
-      <c r="AB60" t="inlineStr">
-        <is>
-          <t>11:30</t>
+          <t>2024-05-21</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>I död gran.</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7902,22 +7897,22 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Ola Freijd</t>
+          <t>Lars Gerre</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Ola Freijd</t>
+          <t>Lars Gerre</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>120408193</v>
+        <v>120391898</v>
       </c>
       <c r="B61" t="n">
-        <v>5189</v>
+        <v>5168</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7926,25 +7921,25 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>105930</v>
+        <v>102204</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Grönhjon</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Callidium aeneum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(De Geer, 1775)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7953,23 +7948,23 @@
       <c r="L61" t="inlineStr"/>
       <c r="M61" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Bredmossen, Vg</t>
+          <t>Kjolgran 6 Ö Ledningsmossen, Drängedalen, Vg</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>344249</v>
+        <v>344183</v>
       </c>
       <c r="R61" t="n">
-        <v>6434428</v>
+        <v>6434303</v>
       </c>
       <c r="S61" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7993,17 +7988,22 @@
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>2024-05-21</t>
+          <t>2024-10-06</t>
+        </is>
+      </c>
+      <c r="Z61" t="inlineStr">
+        <is>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2024-05-21</t>
-        </is>
-      </c>
-      <c r="AC61" t="inlineStr">
-        <is>
-          <t>I död gran.</t>
+          <t>2024-10-06</t>
+        </is>
+      </c>
+      <c r="AB61" t="inlineStr">
+        <is>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -8019,12 +8019,12 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Lars Gerre</t>
+          <t>Ola Freijd</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Lars Gerre</t>
+          <t>Ola Freijd</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>

--- a/artfynd/A 9045-2024 artfynd.xlsx
+++ b/artfynd/A 9045-2024 artfynd.xlsx
@@ -7909,7 +7909,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>120391898</v>
+        <v>120391963</v>
       </c>
       <c r="B61" t="n">
         <v>5168</v>
@@ -7954,14 +7954,14 @@
       <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Kjolgran 6 Ö Ledningsmossen, Drängedalen, Vg</t>
+          <t>Kjolgran 8 Ö Ledningsmossen, Drängedalen, Vg</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>344183</v>
+        <v>344145</v>
       </c>
       <c r="R61" t="n">
-        <v>6434303</v>
+        <v>6434343</v>
       </c>
       <c r="S61" t="n">
         <v>25</v>
@@ -7993,7 +7993,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -8003,7 +8003,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -8031,10 +8031,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>120392393</v>
+        <v>120408243</v>
       </c>
       <c r="B62" t="n">
-        <v>57473</v>
+        <v>57336</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -8047,21 +8047,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -8069,23 +8069,23 @@
       <c r="L62" t="inlineStr"/>
       <c r="M62" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Skog 2 NV Bredmossen, Drängedalen , Vg</t>
+          <t>Bredmossen, Vg</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>344222</v>
+        <v>344249</v>
       </c>
       <c r="R62" t="n">
-        <v>6434363</v>
+        <v>6434428</v>
       </c>
       <c r="S62" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -8109,22 +8109,17 @@
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>2024-10-06</t>
-        </is>
-      </c>
-      <c r="Z62" t="inlineStr">
-        <is>
-          <t>11:55</t>
+          <t>2024-05-21</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2024-10-06</t>
-        </is>
-      </c>
-      <c r="AB62" t="inlineStr">
-        <is>
-          <t>11:55</t>
+          <t>2024-05-21</t>
+        </is>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>Ganska färska hack, vid basen av död gran.</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -8139,19 +8134,19 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Ola Freijd</t>
+          <t>Lars Gerre</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Ola Freijd</t>
+          <t>Lars Gerre</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>120392432</v>
+        <v>120392393</v>
       </c>
       <c r="B63" t="n">
         <v>57473</v>
@@ -8195,14 +8190,14 @@
       <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Skog SO Trehörningen, Drängedalen, Vg</t>
+          <t>Skog 2 NV Bredmossen, Drängedalen , Vg</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>343589</v>
+        <v>344222</v>
       </c>
       <c r="R63" t="n">
-        <v>6434074</v>
+        <v>6434363</v>
       </c>
       <c r="S63" t="n">
         <v>25</v>
@@ -8234,7 +8229,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -8244,7 +8239,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -8271,10 +8266,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>120391963</v>
+        <v>120392432</v>
       </c>
       <c r="B64" t="n">
-        <v>5168</v>
+        <v>57473</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -8287,43 +8282,42 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>102204</v>
+        <v>103021</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Grönhjon</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Callidium aeneum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(De Geer, 1775)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
-      <c r="J64" t="inlineStr"/>
       <c r="K64" t="inlineStr"/>
       <c r="L64" t="inlineStr"/>
       <c r="M64" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Kjolgran 8 Ö Ledningsmossen, Drängedalen, Vg</t>
+          <t>Skog SO Trehörningen, Drängedalen, Vg</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>344145</v>
+        <v>343589</v>
       </c>
       <c r="R64" t="n">
-        <v>6434343</v>
+        <v>6434074</v>
       </c>
       <c r="S64" t="n">
         <v>25</v>
@@ -8355,7 +8349,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -8365,7 +8359,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -8374,7 +8368,6 @@
       <c r="AE64" t="b">
         <v>0</v>
       </c>
-      <c r="AF64" t="inlineStr"/>
       <c r="AG64" t="b">
         <v>0</v>
       </c>
@@ -8393,10 +8386,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>120408289</v>
+        <v>120391898</v>
       </c>
       <c r="B65" t="n">
-        <v>57996</v>
+        <v>5168</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -8405,49 +8398,50 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>103044</v>
+        <v>102204</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Grönhjon</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Callidium aeneum</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(De Geer, 1775)</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
+      <c r="J65" t="inlineStr"/>
       <c r="K65" t="inlineStr"/>
       <c r="L65" t="inlineStr"/>
       <c r="M65" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Bredmossen, Vg</t>
+          <t>Kjolgran 6 Ö Ledningsmossen, Drängedalen, Vg</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>344249</v>
+        <v>344183</v>
       </c>
       <c r="R65" t="n">
-        <v>6434428</v>
+        <v>6434303</v>
       </c>
       <c r="S65" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -8471,22 +8465,22 @@
       </c>
       <c r="Y65" t="inlineStr">
         <is>
-          <t>2024-05-21</t>
+          <t>2024-10-06</t>
         </is>
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>2024-05-21</t>
+          <t>2024-10-06</t>
         </is>
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -8495,28 +8489,29 @@
       <c r="AE65" t="b">
         <v>0</v>
       </c>
+      <c r="AF65" t="inlineStr"/>
       <c r="AG65" t="b">
         <v>0</v>
       </c>
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Lars Gerre</t>
+          <t>Ola Freijd</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Lars Gerre</t>
+          <t>Ola Freijd</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>120408243</v>
+        <v>120408289</v>
       </c>
       <c r="B66" t="n">
-        <v>57336</v>
+        <v>57996</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -8525,20 +8520,20 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>100049</v>
+        <v>103044</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -8551,7 +8546,7 @@
       <c r="L66" t="inlineStr"/>
       <c r="M66" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N66" t="inlineStr"/>
@@ -8594,14 +8589,19 @@
           <t>2024-05-21</t>
         </is>
       </c>
+      <c r="Z66" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
       <c r="AA66" t="inlineStr">
         <is>
           <t>2024-05-21</t>
         </is>
       </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>Ganska färska hack, vid basen av död gran.</t>
+      <c r="AB66" t="inlineStr">
+        <is>
+          <t>18:00</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8862,10 +8862,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>120419661</v>
+        <v>120419699</v>
       </c>
       <c r="B69" t="n">
-        <v>5189</v>
+        <v>57689</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8878,16 +8878,16 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>105930</v>
+        <v>103015</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -8895,13 +8895,16 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I69" t="inlineStr"/>
-      <c r="J69" t="inlineStr"/>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K69" t="inlineStr"/>
       <c r="L69" t="inlineStr"/>
       <c r="M69" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N69" t="inlineStr"/>
@@ -8944,14 +8947,19 @@
           <t>2024-05-21</t>
         </is>
       </c>
+      <c r="Z69" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
       <c r="AA69" t="inlineStr">
         <is>
           <t>2024-05-21</t>
         </is>
       </c>
-      <c r="AC69" t="inlineStr">
-        <is>
-          <t>I död gran,</t>
+      <c r="AB69" t="inlineStr">
+        <is>
+          <t>18:30</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8960,7 +8968,6 @@
       <c r="AE69" t="b">
         <v>0</v>
       </c>
-      <c r="AF69" t="inlineStr"/>
       <c r="AG69" t="b">
         <v>0</v>
       </c>
@@ -8979,10 +8986,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>120419699</v>
+        <v>120419661</v>
       </c>
       <c r="B70" t="n">
-        <v>57689</v>
+        <v>5189</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8995,16 +9002,16 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>103015</v>
+        <v>105930</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -9012,16 +9019,13 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I70" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I70" t="inlineStr"/>
+      <c r="J70" t="inlineStr"/>
       <c r="K70" t="inlineStr"/>
       <c r="L70" t="inlineStr"/>
       <c r="M70" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N70" t="inlineStr"/>
@@ -9064,19 +9068,14 @@
           <t>2024-05-21</t>
         </is>
       </c>
-      <c r="Z70" t="inlineStr">
-        <is>
-          <t>18:00</t>
-        </is>
-      </c>
       <c r="AA70" t="inlineStr">
         <is>
           <t>2024-05-21</t>
         </is>
       </c>
-      <c r="AB70" t="inlineStr">
-        <is>
-          <t>18:30</t>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>I död gran,</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -9085,6 +9084,7 @@
       <c r="AE70" t="b">
         <v>0</v>
       </c>
+      <c r="AF70" t="inlineStr"/>
       <c r="AG70" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 9045-2024 artfynd.xlsx
+++ b/artfynd/A 9045-2024 artfynd.xlsx
@@ -7792,10 +7792,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>120408193</v>
+        <v>120391922</v>
       </c>
       <c r="B60" t="n">
-        <v>5189</v>
+        <v>5168</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7804,25 +7804,25 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>105930</v>
+        <v>102204</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Grönhjon</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Callidium aeneum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(De Geer, 1775)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -7831,23 +7831,23 @@
       <c r="L60" t="inlineStr"/>
       <c r="M60" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Bredmossen, Vg</t>
+          <t>Kjolgran 7 Ö Ledningsmossen, Drängedalen, Vg</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>344249</v>
+        <v>344183</v>
       </c>
       <c r="R60" t="n">
-        <v>6434428</v>
+        <v>6434312</v>
       </c>
       <c r="S60" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7871,17 +7871,22 @@
       </c>
       <c r="Y60" t="inlineStr">
         <is>
-          <t>2024-05-21</t>
+          <t>2024-10-06</t>
+        </is>
+      </c>
+      <c r="Z60" t="inlineStr">
+        <is>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>2024-05-21</t>
-        </is>
-      </c>
-      <c r="AC60" t="inlineStr">
-        <is>
-          <t>I död gran.</t>
+          <t>2024-10-06</t>
+        </is>
+      </c>
+      <c r="AB60" t="inlineStr">
+        <is>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7897,22 +7902,22 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Lars Gerre</t>
+          <t>Ola Freijd</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Lars Gerre</t>
+          <t>Ola Freijd</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>120391963</v>
+        <v>120408193</v>
       </c>
       <c r="B61" t="n">
-        <v>5168</v>
+        <v>5189</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7921,25 +7926,25 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>102204</v>
+        <v>105930</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Grönhjon</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Callidium aeneum</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(De Geer, 1775)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7948,23 +7953,23 @@
       <c r="L61" t="inlineStr"/>
       <c r="M61" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Kjolgran 8 Ö Ledningsmossen, Drängedalen, Vg</t>
+          <t>Bredmossen, Vg</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>344145</v>
+        <v>344249</v>
       </c>
       <c r="R61" t="n">
-        <v>6434343</v>
+        <v>6434428</v>
       </c>
       <c r="S61" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7988,22 +7993,17 @@
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>2024-10-06</t>
-        </is>
-      </c>
-      <c r="Z61" t="inlineStr">
-        <is>
-          <t>13:10</t>
+          <t>2024-05-21</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2024-10-06</t>
-        </is>
-      </c>
-      <c r="AB61" t="inlineStr">
-        <is>
-          <t>13:10</t>
+          <t>2024-05-21</t>
+        </is>
+      </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>I död gran.</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -8019,22 +8019,22 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Ola Freijd</t>
+          <t>Lars Gerre</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Ola Freijd</t>
+          <t>Lars Gerre</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>120408243</v>
+        <v>120392432</v>
       </c>
       <c r="B62" t="n">
-        <v>57336</v>
+        <v>57473</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -8047,21 +8047,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -8069,23 +8069,23 @@
       <c r="L62" t="inlineStr"/>
       <c r="M62" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Bredmossen, Vg</t>
+          <t>Skog SO Trehörningen, Drängedalen, Vg</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>344249</v>
+        <v>343589</v>
       </c>
       <c r="R62" t="n">
-        <v>6434428</v>
+        <v>6434074</v>
       </c>
       <c r="S62" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -8109,17 +8109,22 @@
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>2024-05-21</t>
+          <t>2024-10-06</t>
+        </is>
+      </c>
+      <c r="Z62" t="inlineStr">
+        <is>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2024-05-21</t>
-        </is>
-      </c>
-      <c r="AC62" t="inlineStr">
-        <is>
-          <t>Ganska färska hack, vid basen av död gran.</t>
+          <t>2024-10-06</t>
+        </is>
+      </c>
+      <c r="AB62" t="inlineStr">
+        <is>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -8134,22 +8139,22 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Lars Gerre</t>
+          <t>Ola Freijd</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Lars Gerre</t>
+          <t>Ola Freijd</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>120392393</v>
+        <v>120408243</v>
       </c>
       <c r="B63" t="n">
-        <v>57473</v>
+        <v>57336</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -8162,21 +8167,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -8184,23 +8189,23 @@
       <c r="L63" t="inlineStr"/>
       <c r="M63" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Skog 2 NV Bredmossen, Drängedalen , Vg</t>
+          <t>Bredmossen, Vg</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>344222</v>
+        <v>344249</v>
       </c>
       <c r="R63" t="n">
-        <v>6434363</v>
+        <v>6434428</v>
       </c>
       <c r="S63" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -8224,22 +8229,17 @@
       </c>
       <c r="Y63" t="inlineStr">
         <is>
-          <t>2024-10-06</t>
-        </is>
-      </c>
-      <c r="Z63" t="inlineStr">
-        <is>
-          <t>11:55</t>
+          <t>2024-05-21</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>2024-10-06</t>
-        </is>
-      </c>
-      <c r="AB63" t="inlineStr">
-        <is>
-          <t>11:55</t>
+          <t>2024-05-21</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>Ganska färska hack, vid basen av död gran.</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -8254,19 +8254,19 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Ola Freijd</t>
+          <t>Lars Gerre</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Ola Freijd</t>
+          <t>Lars Gerre</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>120392432</v>
+        <v>120392393</v>
       </c>
       <c r="B64" t="n">
         <v>57473</v>
@@ -8310,14 +8310,14 @@
       <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Skog SO Trehörningen, Drängedalen, Vg</t>
+          <t>Skog 2 NV Bredmossen, Drängedalen , Vg</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>343589</v>
+        <v>344222</v>
       </c>
       <c r="R64" t="n">
-        <v>6434074</v>
+        <v>6434363</v>
       </c>
       <c r="S64" t="n">
         <v>25</v>
@@ -8349,7 +8349,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -8359,7 +8359,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -8386,10 +8386,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>120391898</v>
+        <v>120408289</v>
       </c>
       <c r="B65" t="n">
-        <v>5168</v>
+        <v>57996</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -8398,50 +8398,49 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>102204</v>
+        <v>103044</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Grönhjon</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Callidium aeneum</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(De Geer, 1775)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
-      <c r="J65" t="inlineStr"/>
       <c r="K65" t="inlineStr"/>
       <c r="L65" t="inlineStr"/>
       <c r="M65" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Kjolgran 6 Ö Ledningsmossen, Drängedalen, Vg</t>
+          <t>Bredmossen, Vg</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>344183</v>
+        <v>344249</v>
       </c>
       <c r="R65" t="n">
-        <v>6434303</v>
+        <v>6434428</v>
       </c>
       <c r="S65" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -8465,22 +8464,22 @@
       </c>
       <c r="Y65" t="inlineStr">
         <is>
-          <t>2024-10-06</t>
+          <t>2024-05-21</t>
         </is>
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>2024-10-06</t>
+          <t>2024-05-21</t>
         </is>
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -8489,29 +8488,28 @@
       <c r="AE65" t="b">
         <v>0</v>
       </c>
-      <c r="AF65" t="inlineStr"/>
       <c r="AG65" t="b">
         <v>0</v>
       </c>
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Ola Freijd</t>
+          <t>Lars Gerre</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Ola Freijd</t>
+          <t>Lars Gerre</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>120408289</v>
+        <v>120391963</v>
       </c>
       <c r="B66" t="n">
-        <v>57996</v>
+        <v>5168</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -8520,49 +8518,50 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>103044</v>
+        <v>102204</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Grönhjon</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Callidium aeneum</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(De Geer, 1775)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
+      <c r="J66" t="inlineStr"/>
       <c r="K66" t="inlineStr"/>
       <c r="L66" t="inlineStr"/>
       <c r="M66" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Bredmossen, Vg</t>
+          <t>Kjolgran 8 Ö Ledningsmossen, Drängedalen, Vg</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>344249</v>
+        <v>344145</v>
       </c>
       <c r="R66" t="n">
-        <v>6434428</v>
+        <v>6434343</v>
       </c>
       <c r="S66" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -8586,22 +8585,22 @@
       </c>
       <c r="Y66" t="inlineStr">
         <is>
-          <t>2024-05-21</t>
+          <t>2024-10-06</t>
         </is>
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>2024-05-21</t>
+          <t>2024-10-06</t>
         </is>
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8610,25 +8609,26 @@
       <c r="AE66" t="b">
         <v>0</v>
       </c>
+      <c r="AF66" t="inlineStr"/>
       <c r="AG66" t="b">
         <v>0</v>
       </c>
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Lars Gerre</t>
+          <t>Ola Freijd</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Lars Gerre</t>
+          <t>Ola Freijd</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>120391922</v>
+        <v>120391898</v>
       </c>
       <c r="B67" t="n">
         <v>5168</v>
@@ -8673,14 +8673,14 @@
       <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Kjolgran 7 Ö Ledningsmossen, Drängedalen, Vg</t>
+          <t>Kjolgran 6 Ö Ledningsmossen, Drängedalen, Vg</t>
         </is>
       </c>
       <c r="Q67" t="n">
         <v>344183</v>
       </c>
       <c r="R67" t="n">
-        <v>6434312</v>
+        <v>6434303</v>
       </c>
       <c r="S67" t="n">
         <v>25</v>
@@ -8712,7 +8712,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -8722,7 +8722,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AD67" t="b">

--- a/artfynd/A 9045-2024 artfynd.xlsx
+++ b/artfynd/A 9045-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY71"/>
+  <dimension ref="A1:AY73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9230,6 +9230,251 @@
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>123819752</v>
+      </c>
+      <c r="B72" t="n">
+        <v>56697</v>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
+      <c r="K72" t="inlineStr"/>
+      <c r="L72" t="inlineStr"/>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N72" t="inlineStr"/>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>Häll 4 NO Ledningsmossen, Drängedalen, Vg</t>
+        </is>
+      </c>
+      <c r="Q72" t="n">
+        <v>344000</v>
+      </c>
+      <c r="R72" t="n">
+        <v>6434259</v>
+      </c>
+      <c r="S72" t="n">
+        <v>25</v>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W72" t="inlineStr">
+        <is>
+          <t>Hålanda</t>
+        </is>
+      </c>
+      <c r="Y72" t="inlineStr">
+        <is>
+          <t>2025-03-09</t>
+        </is>
+      </c>
+      <c r="Z72" t="inlineStr">
+        <is>
+          <t>13:15</t>
+        </is>
+      </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>2025-03-09</t>
+        </is>
+      </c>
+      <c r="AB72" t="inlineStr">
+        <is>
+          <t>13:15</t>
+        </is>
+      </c>
+      <c r="AD72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT72" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>Ola Freijd</t>
+        </is>
+      </c>
+      <c r="AX72" t="inlineStr">
+        <is>
+          <t>Ola Freijd</t>
+        </is>
+      </c>
+      <c r="AY72" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>123819735</v>
+      </c>
+      <c r="B73" t="n">
+        <v>58165</v>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>103044</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Grönsiska</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Spinus spinus</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
+      <c r="K73" t="inlineStr"/>
+      <c r="L73" t="inlineStr"/>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N73" t="inlineStr"/>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>Skog 2 NV Bredmossen, Drängedalen , Vg</t>
+        </is>
+      </c>
+      <c r="Q73" t="n">
+        <v>344222</v>
+      </c>
+      <c r="R73" t="n">
+        <v>6434363</v>
+      </c>
+      <c r="S73" t="n">
+        <v>25</v>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W73" t="inlineStr">
+        <is>
+          <t>Hålanda</t>
+        </is>
+      </c>
+      <c r="Y73" t="inlineStr">
+        <is>
+          <t>2025-03-09</t>
+        </is>
+      </c>
+      <c r="Z73" t="inlineStr">
+        <is>
+          <t>12:15</t>
+        </is>
+      </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>2025-03-09</t>
+        </is>
+      </c>
+      <c r="AB73" t="inlineStr">
+        <is>
+          <t>12:15</t>
+        </is>
+      </c>
+      <c r="AC73" t="inlineStr">
+        <is>
+          <t>Flera stycken, minst en sjöng.</t>
+        </is>
+      </c>
+      <c r="AD73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT73" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>Ola Freijd</t>
+        </is>
+      </c>
+      <c r="AX73" t="inlineStr">
+        <is>
+          <t>Ola Freijd</t>
+        </is>
+      </c>
+      <c r="AY73" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 9045-2024 artfynd.xlsx
+++ b/artfynd/A 9045-2024 artfynd.xlsx
@@ -9235,7 +9235,7 @@
         <v>123819752</v>
       </c>
       <c r="B72" t="n">
-        <v>56697</v>
+        <v>56700</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -9355,7 +9355,7 @@
         <v>123819735</v>
       </c>
       <c r="B73" t="n">
-        <v>58165</v>
+        <v>58168</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>

--- a/artfynd/A 9045-2024 artfynd.xlsx
+++ b/artfynd/A 9045-2024 artfynd.xlsx
@@ -9232,10 +9232,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>123819752</v>
+        <v>123819735</v>
       </c>
       <c r="B72" t="n">
-        <v>56700</v>
+        <v>58169</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -9248,21 +9248,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>100138</v>
+        <v>103044</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -9270,20 +9270,20 @@
       <c r="L72" t="inlineStr"/>
       <c r="M72" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Häll 4 NO Ledningsmossen, Drängedalen, Vg</t>
+          <t>Skog 2 NV Bredmossen, Drängedalen , Vg</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>344000</v>
+        <v>344222</v>
       </c>
       <c r="R72" t="n">
-        <v>6434259</v>
+        <v>6434363</v>
       </c>
       <c r="S72" t="n">
         <v>25</v>
@@ -9315,7 +9315,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -9325,7 +9325,12 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>12:15</t>
+        </is>
+      </c>
+      <c r="AC72" t="inlineStr">
+        <is>
+          <t>Flera stycken, minst en sjöng.</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -9352,10 +9357,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>123819735</v>
+        <v>123819752</v>
       </c>
       <c r="B73" t="n">
-        <v>58168</v>
+        <v>56700</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -9368,21 +9373,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>103044</v>
+        <v>100138</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -9390,20 +9395,20 @@
       <c r="L73" t="inlineStr"/>
       <c r="M73" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="N73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Skog 2 NV Bredmossen, Drängedalen , Vg</t>
+          <t>Häll 4 NO Ledningsmossen, Drängedalen, Vg</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>344222</v>
+        <v>344000</v>
       </c>
       <c r="R73" t="n">
-        <v>6434363</v>
+        <v>6434259</v>
       </c>
       <c r="S73" t="n">
         <v>25</v>
@@ -9435,7 +9440,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -9445,12 +9450,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>12:15</t>
-        </is>
-      </c>
-      <c r="AC73" t="inlineStr">
-        <is>
-          <t>Flera stycken, minst en sjöng.</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AD73" t="b">

--- a/artfynd/A 9045-2024 artfynd.xlsx
+++ b/artfynd/A 9045-2024 artfynd.xlsx
@@ -9232,10 +9232,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>123819735</v>
+        <v>123819752</v>
       </c>
       <c r="B72" t="n">
-        <v>58191</v>
+        <v>56722</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -9248,21 +9248,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>103044</v>
+        <v>100138</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -9270,20 +9270,20 @@
       <c r="L72" t="inlineStr"/>
       <c r="M72" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Skog 2 NV Bredmossen, Drängedalen , Vg</t>
+          <t>Häll 4 NO Ledningsmossen, Drängedalen, Vg</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>344222</v>
+        <v>344000</v>
       </c>
       <c r="R72" t="n">
-        <v>6434363</v>
+        <v>6434259</v>
       </c>
       <c r="S72" t="n">
         <v>25</v>
@@ -9315,7 +9315,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -9325,12 +9325,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>12:15</t>
-        </is>
-      </c>
-      <c r="AC72" t="inlineStr">
-        <is>
-          <t>Flera stycken, minst en sjöng.</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -9357,10 +9352,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>123819752</v>
+        <v>123819735</v>
       </c>
       <c r="B73" t="n">
-        <v>56722</v>
+        <v>58191</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -9373,21 +9368,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>100138</v>
+        <v>103044</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -9395,20 +9390,20 @@
       <c r="L73" t="inlineStr"/>
       <c r="M73" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Häll 4 NO Ledningsmossen, Drängedalen, Vg</t>
+          <t>Skog 2 NV Bredmossen, Drängedalen , Vg</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>344000</v>
+        <v>344222</v>
       </c>
       <c r="R73" t="n">
-        <v>6434259</v>
+        <v>6434363</v>
       </c>
       <c r="S73" t="n">
         <v>25</v>
@@ -9440,7 +9435,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -9450,7 +9445,12 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>12:15</t>
+        </is>
+      </c>
+      <c r="AC73" t="inlineStr">
+        <is>
+          <t>Flera stycken, minst en sjöng.</t>
         </is>
       </c>
       <c r="AD73" t="b">

--- a/artfynd/A 9045-2024 artfynd.xlsx
+++ b/artfynd/A 9045-2024 artfynd.xlsx
@@ -6549,12 +6549,7 @@
         <v>118755601</v>
       </c>
       <c r="B50" t="n">
-        <v>5166</v>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5175</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -7915,12 +7910,7 @@
         <v>120391963</v>
       </c>
       <c r="B61" t="n">
-        <v>5168</v>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5175</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -8389,12 +8379,7 @@
         <v>120391922</v>
       </c>
       <c r="B65" t="n">
-        <v>5168</v>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5175</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8631,12 +8616,7 @@
         <v>120391898</v>
       </c>
       <c r="B67" t="n">
-        <v>5168</v>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5175</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>

--- a/artfynd/A 9045-2024 artfynd.xlsx
+++ b/artfynd/A 9045-2024 artfynd.xlsx
@@ -6549,7 +6549,7 @@
         <v>118755601</v>
       </c>
       <c r="B50" t="n">
-        <v>5175</v>
+        <v>5176</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -7910,7 +7910,7 @@
         <v>120391963</v>
       </c>
       <c r="B61" t="n">
-        <v>5175</v>
+        <v>5176</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -8379,7 +8379,7 @@
         <v>120391922</v>
       </c>
       <c r="B65" t="n">
-        <v>5175</v>
+        <v>5176</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8616,7 +8616,7 @@
         <v>120391898</v>
       </c>
       <c r="B67" t="n">
-        <v>5175</v>
+        <v>5176</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>

--- a/artfynd/A 9045-2024 artfynd.xlsx
+++ b/artfynd/A 9045-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY73"/>
+  <dimension ref="A1:AY92"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>115511988</v>
+        <v>115587629</v>
       </c>
       <c r="B2" t="n">
-        <v>95923</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96708</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,41 +686,49 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2569</v>
+        <v>2180</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Trehörningen, Vg</t>
+          <t>Långesjön, norr om, Vg</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>343772</v>
+        <v>343983</v>
       </c>
       <c r="R2" t="n">
-        <v>6434108</v>
+        <v>6434270</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -749,22 +752,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-03-29</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>12:30</t>
+          <t>2024-03-26</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-03-29</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>16:00</t>
+          <t>2024-03-26</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>En kudde som var ca 35 cm hög, 50 cm lång och 45 cm bred.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -780,55 +778,50 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Ann-Charlotte Svensson</t>
+          <t>Thomas Grönlund</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Ann-Charlotte Svensson</t>
+          <t>Thomas Grönlund</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>115511970</v>
+        <v>115511988</v>
       </c>
       <c r="B3" t="n">
-        <v>57281</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97733</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>2569</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -890,79 +883,79 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Ann-Charlotte Svensson</t>
+          <t>Anna Svensson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Ann-Charlotte Svensson</t>
+          <t>Anna Svensson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>115587706</v>
+        <v>116013525</v>
       </c>
       <c r="B4" t="n">
-        <v>57281</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97733</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>2569</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(L.) Gray</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Långesjön, norr om, Vg</t>
+          <t>Långesjön, nordost om, Vg</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>344038</v>
+        <v>344195</v>
       </c>
       <c r="R4" t="n">
-        <v>6434276</v>
+        <v>6434451</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -986,17 +979,27 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-03-26</t>
+          <t>2024-04-15</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-03-26</t>
+          <t>2024-04-15</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Spillkråkehack efter födosök vid basen av en stam.</t>
+          <t>Noterade ca 3 kvm med stor revmossa inom en radie av 10 m. Sannolikt fanns mer i detta område.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1005,6 +1008,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1023,51 +1027,46 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>115587680</v>
+        <v>116022204</v>
       </c>
       <c r="B5" t="n">
-        <v>57281</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97733</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>2569</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>dm²</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1075,10 +1074,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>343742</v>
+        <v>343801</v>
       </c>
       <c r="R5" t="n">
-        <v>6434133</v>
+        <v>6434140</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1105,17 +1104,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-03-26</t>
+          <t>2024-04-15</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-03-26</t>
+          <t>2024-04-15</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Spillkråkehack efter födosök vid basen av en gran.</t>
+          <t>I den östvända branten ner mot våtmarken.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1124,6 +1123,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1142,15 +1142,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>115587629</v>
+        <v>117123406</v>
       </c>
       <c r="B6" t="n">
-        <v>94429</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97733</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1158,21 +1153,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2180</v>
+        <v>2569</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1182,7 +1177,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
@@ -1190,14 +1185,14 @@
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Långesjön, norr om, Vg</t>
+          <t>Långesjön, nordost om, Vg</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>343983</v>
+        <v>343924</v>
       </c>
       <c r="R6" t="n">
-        <v>6434270</v>
+        <v>6434315</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1224,17 +1219,27 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-03-26</t>
+          <t>2024-05-18</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-03-26</t>
+          <t>2024-05-18</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>En kudde som var ca 35 cm hög, 50 cm lång och 45 cm bred.</t>
+          <t>Vid foten av en klibbal.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1262,15 +1267,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>115941784</v>
+        <v>117148040</v>
       </c>
       <c r="B7" t="n">
-        <v>8403</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97733</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1278,28 +1278,35 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>106554</v>
+        <v>2569</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
+          <t>(L.) Gray</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1307,10 +1314,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>344002</v>
+        <v>343793</v>
       </c>
       <c r="R7" t="n">
-        <v>6434216</v>
+        <v>6434100</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1337,17 +1344,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-03-26</t>
+          <t>2024-05-18</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-03-26</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Noterade flera rader med hål från björksplintborre på en björkhögstubbe.</t>
+          <t>2024-05-18</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1375,15 +1377,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>116012544</v>
+        <v>120419793</v>
       </c>
       <c r="B8" t="n">
-        <v>57624</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97733</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1391,46 +1388,38 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103015</v>
+        <v>2569</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) Gray</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Långesjön, nordost om, Vg</t>
+          <t>Trehörningen, sydost om, Vg</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>344262</v>
+        <v>343605</v>
       </c>
       <c r="R8" t="n">
-        <v>6434376</v>
+        <v>6434107</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1457,17 +1446,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-04-15</t>
+          <t>2024-05-21</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-04-15</t>
+          <t>2024-05-21</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>I mossekanten</t>
+          <t>Några större tuvor.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1476,33 +1465,29 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Thomas Grönlund</t>
+          <t>Lars Gerre</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Thomas Grönlund</t>
+          <t>Lars Gerre</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>116022204</v>
+        <v>116021736</v>
       </c>
       <c r="B9" t="n">
-        <v>95932</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97785</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1510,26 +1495,26 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2569</v>
+        <v>2606</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1542,14 +1527,14 @@
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Långesjön, norr om, Vg</t>
+          <t>Långesjön, nordost om, Vg</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>343801</v>
+        <v>343922</v>
       </c>
       <c r="R9" t="n">
-        <v>6434140</v>
+        <v>6434313</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1586,7 +1571,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>I den östvända branten ner mot våtmarken.</t>
+          <t>Noterade arten på en av de båda klibbalarna i sumpskogen.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1614,15 +1599,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>116015654</v>
+        <v>117123446</v>
       </c>
       <c r="B10" t="n">
-        <v>8403</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97785</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1630,32 +1610,35 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>106554</v>
+        <v>2606</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
+          <t>(L.) Dumort.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1663,10 +1646,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>343919</v>
+        <v>343914</v>
       </c>
       <c r="R10" t="n">
-        <v>6434319</v>
+        <v>6434332</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1693,7 +1676,7 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2024-04-15</t>
+          <t>2024-05-18</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
@@ -1703,7 +1686,7 @@
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2024-04-15</t>
+          <t>2024-05-18</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -1713,7 +1696,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Rader med hål efter björksplintborren i en 5 m hög björkhögstubbe.</t>
+          <t>Växte på stammen hos en äldre klibbal i sumpskogen.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1741,47 +1724,46 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>116013939</v>
+        <v>117123515</v>
       </c>
       <c r="B11" t="n">
-        <v>57281</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97785</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>2606</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(L.) Dumort.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1789,10 +1771,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>344182</v>
+        <v>343905</v>
       </c>
       <c r="R11" t="n">
-        <v>6434452</v>
+        <v>6434339</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1819,7 +1801,7 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2024-04-15</t>
+          <t>2024-05-18</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
@@ -1829,7 +1811,7 @@
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2024-04-15</t>
+          <t>2024-05-18</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -1839,7 +1821,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Hack vid basen av en högstubbe av en medelgrov tall.</t>
+          <t>Växte på stammen hos en två äldre medelgrova klibbalar samt en björk i sumpskogen. Träden stod inom några meter från varandra.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1848,6 +1830,7 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1866,61 +1849,52 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>116012585</v>
+        <v>119447676</v>
       </c>
       <c r="B12" t="n">
-        <v>57281</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96348</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>2810</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Långesjön, nordost om, Vg</t>
+          <t>Kant mot hygge NV Bredmossen, Drängedalen , Vg</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>344239</v>
+        <v>344144</v>
       </c>
       <c r="R12" t="n">
-        <v>6434359</v>
+        <v>6434438</v>
       </c>
       <c r="S12" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1944,17 +1918,27 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2024-04-15</t>
+          <t>2024-08-12</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2024-04-15</t>
+          <t>2024-08-12</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Fann spillkråkehack vid basen av ett torrträd av en medelgrov tall.</t>
+          <t>Mycket.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1963,33 +1947,29 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Thomas Grönlund</t>
+          <t>Ola Freijd</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Thomas Grönlund</t>
+          <t>Ola Freijd</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>116013525</v>
+        <v>115511970</v>
       </c>
       <c r="B13" t="n">
-        <v>95932</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1997,46 +1977,38 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2569</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Långesjön, nordost om, Vg</t>
+          <t>Trehörningen, Vg</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>344195</v>
+        <v>343772</v>
       </c>
       <c r="R13" t="n">
-        <v>6434451</v>
+        <v>6434108</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2063,27 +2035,22 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2024-04-15</t>
+          <t>2024-03-29</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2024-04-15</t>
+          <t>2024-03-29</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Noterade ca 3 kvm med stor revmossa inom en radie av 10 m. Sannolikt fanns mer i detta område.</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2092,34 +2059,28 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Thomas Grönlund</t>
+          <t>Anna Svensson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Thomas Grönlund</t>
+          <t>Anna Svensson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>116015428</v>
+        <v>115587680</v>
       </c>
       <c r="B14" t="n">
-        <v>8403</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2127,43 +2088,46 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>106554</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Långesjön, nordost om, Vg</t>
+          <t>Långesjön, norr om, Vg</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>344140</v>
+        <v>343742</v>
       </c>
       <c r="R14" t="n">
-        <v>6434310</v>
+        <v>6434133</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2190,27 +2154,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2024-04-15</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-03-26</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2024-04-15</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-03-26</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Rader med hål efter björksplintborren i en 5 m hög björkhögstubbe.</t>
+          <t>Spillkråkehack efter födosök vid basen av en gran.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2219,7 +2173,6 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2238,19 +2191,14 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>116014729</v>
+        <v>115587706</v>
       </c>
       <c r="B15" t="n">
-        <v>57281</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
@@ -2282,14 +2230,14 @@
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Långesjön, nordost om, Vg</t>
+          <t>Långesjön, norr om, Vg</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>344201</v>
+        <v>344038</v>
       </c>
       <c r="R15" t="n">
-        <v>6434419</v>
+        <v>6434276</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2316,27 +2264,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2024-04-15</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-03-26</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2024-04-15</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-03-26</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Spillkråkehack vid basen av en medelgrov högstubbe av tall.</t>
+          <t>Spillkråkehack efter födosök vid basen av en stam.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2363,15 +2301,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>116018621</v>
+        <v>116012585</v>
       </c>
       <c r="B16" t="n">
-        <v>5185</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2379,16 +2312,16 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>105930</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -2397,25 +2330,24 @@
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Långesjön, norr om, Vg</t>
+          <t>Långesjön, nordost om, Vg</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>343562</v>
+        <v>344239</v>
       </c>
       <c r="R16" t="n">
-        <v>6434089</v>
+        <v>6434359</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2445,24 +2377,14 @@
           <t>2024-04-15</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2024-04-15</t>
         </is>
       </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Spår på ett 15 cm tjockt torrträd av gran som stod i kanten av våtmarken.</t>
+          <t>Fann spillkråkehack vid basen av ett torrträd av en medelgrov tall.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2471,7 +2393,6 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2490,15 +2411,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>116015609</v>
+        <v>116013939</v>
       </c>
       <c r="B17" t="n">
-        <v>8403</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2506,30 +2422,29 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>106554</v>
+        <v>100049</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N17" t="inlineStr"/>
@@ -2539,10 +2454,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>344051</v>
+        <v>344182</v>
       </c>
       <c r="R17" t="n">
-        <v>6434289</v>
+        <v>6434452</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2589,7 +2504,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Rader med hål efter björksplintborren i en 4 m hög björkhögstubbe.</t>
+          <t>Hack vid basen av en högstubbe av en medelgrov tall.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2598,7 +2513,6 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2617,15 +2531,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>116015635</v>
+        <v>116014729</v>
       </c>
       <c r="B18" t="n">
-        <v>8403</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2633,30 +2542,29 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>106554</v>
+        <v>100049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N18" t="inlineStr"/>
@@ -2666,10 +2574,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>343919</v>
+        <v>344201</v>
       </c>
       <c r="R18" t="n">
-        <v>6434275</v>
+        <v>6434419</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2716,7 +2624,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Rader med hål efter björksplintborren i en 6 m hög björkhögstubbe.</t>
+          <t>Spillkråkehack vid basen av en medelgrov högstubbe av tall.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2725,7 +2633,6 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2744,15 +2651,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>116021691</v>
+        <v>116016843</v>
       </c>
       <c r="B19" t="n">
-        <v>57916</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2760,16 +2662,16 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>103044</v>
+        <v>100049</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -2777,16 +2679,12 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
-          <t>förbiflygande</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N19" t="inlineStr"/>
@@ -2796,13 +2694,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>344243</v>
+        <v>344037</v>
       </c>
       <c r="R19" t="n">
-        <v>6434390</v>
+        <v>6434274</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2829,14 +2727,24 @@
           <t>2024-04-15</t>
         </is>
       </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2024-04-15</t>
         </is>
       </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Hörde en handfull grönsiskor över mig i trädhöjd när jag kollade kantvitmossan.</t>
+          <t>Spillkråkehack efter spillkråka vid basen av ett medelgrovt torrträd av gran.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2863,15 +2771,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>116018541</v>
+        <v>116017288</v>
       </c>
       <c r="B20" t="n">
-        <v>5185</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2879,16 +2782,16 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>105930</v>
+        <v>100049</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2897,12 +2800,11 @@
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N20" t="inlineStr"/>
@@ -2912,10 +2814,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>343925</v>
+        <v>343801</v>
       </c>
       <c r="R20" t="n">
-        <v>6434320</v>
+        <v>6434140</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2962,7 +2864,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Spår på en gran i sumpskogen norr om bäcken.</t>
+          <t>Spillkråkehack vid basen av ett talltorrträd.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2971,7 +2873,6 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2990,15 +2891,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>116015307</v>
+        <v>116021537</v>
       </c>
       <c r="B21" t="n">
-        <v>8403</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3006,30 +2902,33 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>106554</v>
+        <v>100049</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N21" t="inlineStr"/>
@@ -3039,13 +2938,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>344154</v>
+        <v>343839</v>
       </c>
       <c r="R21" t="n">
-        <v>6434302</v>
+        <v>6434304</v>
       </c>
       <c r="S21" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3072,24 +2971,14 @@
           <t>2024-04-15</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>09:00</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2024-04-15</t>
         </is>
       </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>09:00</t>
-        </is>
-      </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Rader med hål efter björksplintborren i en 3 m hög björkhögstubbe i sumpskogen.</t>
+          <t>Hörde först en spillkråka komma flygande och landa nära den grova aspen. Var där i någon minut, men flög sedan tillbaka åt samma håll som den kom. Efter ytterligare någon minut hörde jag en spillkråka nära aspen igen, men samtidigt hörde jag den första från nordost. Det var sålunda två individer på platsen, troligen samtidigt, men jag såg bara den ena.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3098,7 +2987,6 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -3117,15 +3005,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>116015720</v>
+        <v>119447415</v>
       </c>
       <c r="B22" t="n">
-        <v>8403</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3133,46 +3016,45 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>106554</v>
+        <v>100049</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Långesjön, nordost om, Vg</t>
+          <t>Skog 150 m NNV Bredmossen, Vg</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>343857</v>
+        <v>344191</v>
       </c>
       <c r="R22" t="n">
-        <v>6434254</v>
+        <v>6434464</v>
       </c>
       <c r="S22" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3196,27 +3078,27 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2024-04-15</t>
+          <t>2024-08-12</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2024-04-15</t>
+          <t>2024-08-12</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Rader med hål efter björksplintborren i en 3 m hög björkhögstubbe.</t>
+          <t>Spår efter födosök i granstam.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3225,34 +3107,28 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Thomas Grönlund</t>
+          <t>Ola Freijd</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Thomas Grönlund</t>
+          <t>Ola Freijd</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>116018500</v>
+        <v>119447662</v>
       </c>
       <c r="B23" t="n">
-        <v>5185</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3260,16 +3136,16 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>105930</v>
+        <v>100049</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -3278,28 +3154,27 @@
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Långesjön, nordost om, Vg</t>
+          <t>Kant mot hygge NV Bredmossen, Drängedalen , Vg</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>343917</v>
+        <v>344144</v>
       </c>
       <c r="R23" t="n">
-        <v>6434318</v>
+        <v>6434438</v>
       </c>
       <c r="S23" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3323,27 +3198,27 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2024-04-15</t>
+          <t>2024-08-12</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2024-04-15</t>
+          <t>2024-08-12</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Spår på ett torrträd av en 15 cm tjock gran.</t>
+          <t>Spår efter födosök i granstubbe.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3352,34 +3227,28 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Thomas Grönlund</t>
+          <t>Ola Freijd</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Thomas Grönlund</t>
+          <t>Ola Freijd</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>116015266</v>
+        <v>119447781</v>
       </c>
       <c r="B24" t="n">
-        <v>8403</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3387,46 +3256,45 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>106554</v>
+        <v>100049</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr"/>
       <c r="M24" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Långesjön, nordost om, Vg</t>
+          <t>Kjolgran SO Långemossen, Drängedalen , Vg</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>344160</v>
+        <v>343964</v>
       </c>
       <c r="R24" t="n">
-        <v>6434320</v>
+        <v>6434348</v>
       </c>
       <c r="S24" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3450,27 +3318,27 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2024-04-15</t>
+          <t>2024-08-12</t>
         </is>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2024-04-15</t>
+          <t>2024-08-12</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Rader med hål i en 2 m hög björkhögstubbe, i kanten på ett blötare parti.</t>
+          <t>Spår efter födosök i död kjolgran.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3479,34 +3347,28 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Thomas Grönlund</t>
+          <t>Ola Freijd</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Thomas Grönlund</t>
+          <t>Ola Freijd</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>116013101</v>
+        <v>119447788</v>
       </c>
       <c r="B25" t="n">
-        <v>57624</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3514,16 +3376,16 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>103015</v>
+        <v>100049</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -3531,25 +3393,25 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Långesjön, nordost om, Vg</t>
+          <t>S om Långemossen 3, Drängedalen, Vg</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>344211</v>
+        <v>343963</v>
       </c>
       <c r="R25" t="n">
-        <v>6434479</v>
+        <v>6434292</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3576,22 +3438,27 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2024-04-15</t>
+          <t>2024-08-12</t>
         </is>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2024-04-15</t>
+          <t>2024-08-12</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>15:05</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Spår efter födosök i torr granstubbe.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3606,27 +3473,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Thomas Grönlund</t>
+          <t>Ola Freijd</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Thomas Grönlund</t>
+          <t>Ola Freijd</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>116021091</v>
+        <v>120408243</v>
       </c>
       <c r="B26" t="n">
-        <v>5185</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3634,16 +3496,16 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>105930</v>
+        <v>100049</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -3652,25 +3514,24 @@
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr"/>
       <c r="M26" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Långesjön, nordost om, Vg</t>
+          <t>Bredmossen, Vg</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>343941</v>
+        <v>344249</v>
       </c>
       <c r="R26" t="n">
-        <v>6434219</v>
+        <v>6434428</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3697,12 +3558,17 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2024-04-15</t>
+          <t>2024-05-21</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2024-04-15</t>
+          <t>2024-05-21</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Ganska färska hack, vid basen av död gran.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3711,84 +3577,78 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Thomas Grönlund</t>
+          <t>Lars Gerre</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Thomas Grönlund</t>
+          <t>Lars Gerre</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>116021736</v>
+        <v>118756709</v>
       </c>
       <c r="B27" t="n">
-        <v>96292</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57838</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>2606</v>
+        <v>100100</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Bivråk</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Pernis apivorus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>dm²</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Långesjön, nordost om, Vg</t>
+          <t>Skog NO Ledningsmossen, Drängedalen, Vg</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>343922</v>
+        <v>343996</v>
       </c>
       <c r="R27" t="n">
-        <v>6434313</v>
+        <v>6434225</v>
       </c>
       <c r="S27" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3812,17 +3672,27 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2024-04-15</t>
+          <t>2024-07-21</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2024-04-15</t>
+          <t>2024-07-21</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Noterade arten på en av de båda klibbalarna i sumpskogen.</t>
+          <t>Rörde sig över Ledningsmossen, ropande.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3831,34 +3701,28 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Thomas Grönlund</t>
+          <t>Ola Freijd</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Thomas Grönlund</t>
+          <t>Ola Freijd</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>116015868</v>
+        <v>116541309</v>
       </c>
       <c r="B28" t="n">
-        <v>8403</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3866,46 +3730,45 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>106554</v>
+        <v>100138</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr"/>
       <c r="M28" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Långesjön, nordost om, Vg</t>
+          <t>Bergrygg N Bredmossen, Drängedalen, Vg</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>343952</v>
+        <v>344254</v>
       </c>
       <c r="R28" t="n">
-        <v>6434174</v>
+        <v>6434389</v>
       </c>
       <c r="S28" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3929,27 +3792,22 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2024-04-15</t>
+          <t>2024-05-02</t>
         </is>
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2024-04-15</t>
+          <t>2024-05-02</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Rader med hål efter björksplintborren i två björkhögstubbar.</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3958,56 +3816,50 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Thomas Grönlund</t>
+          <t>Ola Freijd</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Thomas Grönlund</t>
+          <t>Ola Freijd</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>116017288</v>
+        <v>116541350</v>
       </c>
       <c r="B29" t="n">
-        <v>57281</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -4015,23 +3867,23 @@
       <c r="L29" t="inlineStr"/>
       <c r="M29" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Långesjön, nordost om, Vg</t>
+          <t>Sumpskog NV Bredmossen, NV kanten, Drängedalen, Vg</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>343801</v>
+        <v>344052</v>
       </c>
       <c r="R29" t="n">
-        <v>6434140</v>
+        <v>6434337</v>
       </c>
       <c r="S29" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -4055,27 +3907,27 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2024-04-15</t>
+          <t>2024-05-02</t>
         </is>
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2024-04-15</t>
+          <t>2024-05-02</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Spillkråkehack vid basen av ett talltorrträd.</t>
+          <t>Något äldre.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4090,27 +3942,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Thomas Grönlund</t>
+          <t>Ola Freijd</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Thomas Grönlund</t>
+          <t>Ola Freijd</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>116012504</v>
+        <v>116541360</v>
       </c>
       <c r="B30" t="n">
-        <v>5185</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4118,46 +3965,45 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>105930</v>
+        <v>100138</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr"/>
       <c r="M30" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Långesjön, nordost om, Vg</t>
+          <t>Bergknalle V om Ledningsmossen, Drängedalen, Vg</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>344262</v>
+        <v>343714</v>
       </c>
       <c r="R30" t="n">
-        <v>6434376</v>
+        <v>6434160</v>
       </c>
       <c r="S30" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4181,17 +4027,27 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2024-04-15</t>
+          <t>2024-05-02</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2024-04-15</t>
+          <t>2024-05-02</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Noterade gnagspår på senvuxen klen, tvåtoppig gran i mossekanten</t>
+          <t>Fjäder från tupp, troligen undre stjärttäckare.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4200,56 +4056,50 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Thomas Grönlund</t>
+          <t>Ola Freijd</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Thomas Grönlund</t>
+          <t>Ola Freijd</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>116016843</v>
+        <v>116950327</v>
       </c>
       <c r="B31" t="n">
-        <v>57281</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4257,23 +4107,23 @@
       <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Långesjön, nordost om, Vg</t>
+          <t>Häll NO Ledningsmossen, Drängedalen, Vg</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>344037</v>
+        <v>344030</v>
       </c>
       <c r="R31" t="n">
-        <v>6434274</v>
+        <v>6434257</v>
       </c>
       <c r="S31" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4297,27 +4147,22 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2024-04-15</t>
+          <t>2024-05-12</t>
         </is>
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>07:45</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2024-04-15</t>
+          <t>2024-05-12</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Spillkråkehack efter spillkråka vid basen av ett medelgrovt torrträd av gran.</t>
+          <t>07:45</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4332,27 +4177,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Thomas Grönlund</t>
+          <t>Ola Freijd</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Thomas Grönlund</t>
+          <t>Ola Freijd</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>116541309</v>
+        <v>116950430</v>
       </c>
       <c r="B32" t="n">
-        <v>56491</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4388,14 +4228,14 @@
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Bergrygg N Bredmossen, Drängedalen, Vg</t>
+          <t>Häll vid sumpskog NV Bredmossen, Drängedalen, Vg</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>344254</v>
+        <v>344081</v>
       </c>
       <c r="R32" t="n">
-        <v>6434389</v>
+        <v>6434291</v>
       </c>
       <c r="S32" t="n">
         <v>25</v>
@@ -4422,22 +4262,22 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2024-05-02</t>
+          <t>2024-05-12</t>
         </is>
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2024-05-02</t>
+          <t>2024-05-12</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4464,15 +4304,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>116541360</v>
+        <v>116950473</v>
       </c>
       <c r="B33" t="n">
-        <v>56491</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4502,20 +4337,20 @@
       <c r="L33" t="inlineStr"/>
       <c r="M33" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Bergknalle V om Ledningsmossen, Drängedalen, Vg</t>
+          <t>Häll 2 NV Bredmossen, Drängedalen, Vg</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>343714</v>
+        <v>344147</v>
       </c>
       <c r="R33" t="n">
-        <v>6434160</v>
+        <v>6434364</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>
@@ -4542,27 +4377,27 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2024-05-02</t>
+          <t>2024-05-12</t>
         </is>
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2024-05-02</t>
+          <t>2024-05-12</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Fjäder från tupp, troligen undre stjärttäckare.</t>
+          <t>Något äldre.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4589,15 +4424,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>116541350</v>
+        <v>116950486</v>
       </c>
       <c r="B34" t="n">
-        <v>56491</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4633,14 +4463,14 @@
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Sumpskog NV Bredmossen, NV kanten, Drängedalen, Vg</t>
+          <t>Häll 2 NO Ledningsmossen, Drängedalen, Vg</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>344052</v>
+        <v>344044</v>
       </c>
       <c r="R34" t="n">
-        <v>6434337</v>
+        <v>6434203</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -4667,27 +4497,22 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2024-05-02</t>
+          <t>2024-05-12</t>
         </is>
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2024-05-02</t>
+          <t>2024-05-12</t>
         </is>
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>12:15</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Något äldre.</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4714,15 +4539,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>116950473</v>
+        <v>117106978</v>
       </c>
       <c r="B35" t="n">
-        <v>56491</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4752,20 +4572,20 @@
       <c r="L35" t="inlineStr"/>
       <c r="M35" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Häll 2 NV Bredmossen, Drängedalen, Vg</t>
+          <t>Grästuvor NO Ledningsmossen, Drängedalen, Vg</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>344147</v>
+        <v>344057</v>
       </c>
       <c r="R35" t="n">
-        <v>6434364</v>
+        <v>6434283</v>
       </c>
       <c r="S35" t="n">
         <v>25</v>
@@ -4792,27 +4612,22 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2024-05-12</t>
+          <t>2024-05-17</t>
         </is>
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>08:05</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2024-05-12</t>
+          <t>2024-05-17</t>
         </is>
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>09:00</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Något äldre.</t>
+          <t>08:05</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4839,15 +4654,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>116950430</v>
+        <v>117107082</v>
       </c>
       <c r="B36" t="n">
-        <v>56491</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4877,20 +4687,20 @@
       <c r="L36" t="inlineStr"/>
       <c r="M36" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Häll vid sumpskog NV Bredmossen, Drängedalen, Vg</t>
+          <t>Skog 2 NO Ledningsmossen, Drängedalen, Vg</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>344081</v>
+        <v>343972</v>
       </c>
       <c r="R36" t="n">
-        <v>6434291</v>
+        <v>6434235</v>
       </c>
       <c r="S36" t="n">
         <v>25</v>
@@ -4917,22 +4727,22 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2024-05-12</t>
+          <t>2024-05-17</t>
         </is>
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2024-05-12</t>
+          <t>2024-05-17</t>
         </is>
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4959,15 +4769,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>116950327</v>
+        <v>117146123</v>
       </c>
       <c r="B37" t="n">
-        <v>56491</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4997,23 +4802,23 @@
       <c r="L37" t="inlineStr"/>
       <c r="M37" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Häll NO Ledningsmossen, Drängedalen, Vg</t>
+          <t>Långesjön, norr om, Vg</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>344030</v>
+        <v>343772</v>
       </c>
       <c r="R37" t="n">
-        <v>6434257</v>
+        <v>6434229</v>
       </c>
       <c r="S37" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -5037,22 +4842,17 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2024-05-12</t>
-        </is>
-      </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>07:45</t>
+          <t>2024-05-18</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2024-05-12</t>
-        </is>
-      </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>07:45</t>
+          <t>2024-05-18</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Fann en balgrop med ett fjäderdun från en tjädertupp i en sandig rotvälta.</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5067,27 +4867,22 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Ola Freijd</t>
+          <t>Thomas Grönlund</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Ola Freijd</t>
+          <t>Thomas Grönlund</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>117106978</v>
+        <v>117148586</v>
       </c>
       <c r="B38" t="n">
-        <v>56494</v>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5123,17 +4918,17 @@
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Grästuvor NO Ledningsmossen, Drängedalen, Vg</t>
+          <t>Långesjön, nordost om, Vg</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>344057</v>
+        <v>344201</v>
       </c>
       <c r="R38" t="n">
         <v>6434283</v>
       </c>
       <c r="S38" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -5157,22 +4952,17 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2024-05-17</t>
-        </is>
-      </c>
-      <c r="Z38" t="inlineStr">
-        <is>
-          <t>08:05</t>
+          <t>2024-05-18</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2024-05-17</t>
-        </is>
-      </c>
-      <c r="AB38" t="inlineStr">
-        <is>
-          <t>08:05</t>
+          <t>2024-05-18</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>6 tjäderskitar på en häll.</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5187,27 +4977,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Ola Freijd</t>
+          <t>Thomas Grönlund</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Ola Freijd</t>
+          <t>Thomas Grönlund</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>117107082</v>
+        <v>117551193</v>
       </c>
       <c r="B39" t="n">
-        <v>56494</v>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5234,23 +5019,27 @@
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Skog 2 NO Ledningsmossen, Drängedalen, Vg</t>
+          <t>Sumpskog NV Bredmossen, N kanten, Vg</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>343972</v>
+        <v>344129</v>
       </c>
       <c r="R39" t="n">
-        <v>6434235</v>
+        <v>6434322</v>
       </c>
       <c r="S39" t="n">
         <v>25</v>
@@ -5277,22 +5066,27 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2024-05-17</t>
+          <t>2024-05-29</t>
         </is>
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2024-05-17</t>
+          <t>2024-05-29</t>
         </is>
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Stora skitar på två olika stenar.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5319,15 +5113,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>117137881</v>
+        <v>118207826</v>
       </c>
       <c r="B40" t="n">
-        <v>56497</v>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5335,21 +5124,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>102613</v>
+        <v>100138</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -5357,20 +5146,20 @@
       <c r="L40" t="inlineStr"/>
       <c r="M40" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Häll 4 NO Ledningsmossen, Drängedalen, Vg</t>
+          <t>N spets Bredmossen, Drängedalen, Vg</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>344000</v>
+        <v>344280</v>
       </c>
       <c r="R40" t="n">
-        <v>6434259</v>
+        <v>6434365</v>
       </c>
       <c r="S40" t="n">
         <v>25</v>
@@ -5397,22 +5186,22 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2024-05-17</t>
+          <t>2024-06-29</t>
         </is>
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:25</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2024-05-17</t>
+          <t>2024-06-29</t>
         </is>
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:25</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5439,15 +5228,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>117146123</v>
+        <v>118208072</v>
       </c>
       <c r="B41" t="n">
-        <v>56494</v>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5477,23 +5261,23 @@
       <c r="L41" t="inlineStr"/>
       <c r="M41" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Långesjön, norr om, Vg</t>
+          <t>N om Ledningsmossen, Drängedalen, Vg</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>343772</v>
+        <v>343920</v>
       </c>
       <c r="R41" t="n">
-        <v>6434229</v>
+        <v>6434211</v>
       </c>
       <c r="S41" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5517,17 +5301,22 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2024-05-18</t>
+          <t>2024-06-29</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2024-05-18</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Fann en balgrop med ett fjäderdun från en tjädertupp i en sandig rotvälta.</t>
+          <t>2024-06-29</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5542,27 +5331,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Thomas Grönlund</t>
+          <t>Ola Freijd</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Thomas Grönlund</t>
+          <t>Ola Freijd</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>117123406</v>
+        <v>118756857</v>
       </c>
       <c r="B42" t="n">
-        <v>96068</v>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5570,49 +5354,45 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>2569</v>
+        <v>100138</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
       <c r="K42" t="inlineStr"/>
       <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Långesjön, nordost om, Vg</t>
+          <t>Häll 3 NV Bredmossen, Drängedalen, Vg</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>343924</v>
+        <v>344067</v>
       </c>
       <c r="R42" t="n">
-        <v>6434315</v>
+        <v>6434348</v>
       </c>
       <c r="S42" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5636,27 +5416,22 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2024-05-18</t>
+          <t>2024-07-21</t>
         </is>
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2024-05-18</t>
+          <t>2024-07-21</t>
         </is>
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Vid foten av en klibbal.</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5665,34 +5440,28 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
-      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Thomas Grönlund</t>
+          <t>Ola Freijd</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Thomas Grönlund</t>
+          <t>Ola Freijd</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>117551193</v>
+        <v>119447783</v>
       </c>
       <c r="B43" t="n">
-        <v>56500</v>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5717,7 +5486,11 @@
           <t>Linnaeus, 1758</t>
         </is>
       </c>
-      <c r="I43" t="inlineStr"/>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K43" t="inlineStr"/>
       <c r="L43" t="inlineStr">
         <is>
@@ -5726,20 +5499,20 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Sumpskog NV Bredmossen, N kanten, Vg</t>
+          <t>Kjolgran SO Långemossen, Drängedalen , Vg</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>344129</v>
+        <v>343964</v>
       </c>
       <c r="R43" t="n">
-        <v>6434322</v>
+        <v>6434348</v>
       </c>
       <c r="S43" t="n">
         <v>25</v>
@@ -5766,27 +5539,27 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2024-05-29</t>
+          <t>2024-08-12</t>
         </is>
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2024-05-29</t>
+          <t>2024-08-12</t>
         </is>
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>Stora skitar på två olika stenar.</t>
+          <t>Fjädrar från tupp.</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5813,15 +5586,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>117552948</v>
+        <v>123819752</v>
       </c>
       <c r="B44" t="n">
-        <v>56503</v>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5829,21 +5597,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>102613</v>
+        <v>100138</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5851,20 +5619,20 @@
       <c r="L44" t="inlineStr"/>
       <c r="M44" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Norrkant Ledningsmossen, Drängedalen, Vg</t>
+          <t>Häll 4 NO Ledningsmossen, Drängedalen, Vg</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>343871</v>
+        <v>344000</v>
       </c>
       <c r="R44" t="n">
-        <v>6434192</v>
+        <v>6434259</v>
       </c>
       <c r="S44" t="n">
         <v>25</v>
@@ -5891,22 +5659,22 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2024-05-29</t>
+          <t>2025-03-09</t>
         </is>
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2024-05-29</t>
+          <t>2025-03-09</t>
         </is>
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5933,15 +5701,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>118208072</v>
+        <v>116030367</v>
       </c>
       <c r="B45" t="n">
-        <v>56502</v>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5179</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5949,45 +5712,46 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100138</v>
+        <v>100526</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr"/>
       <c r="K45" t="inlineStr"/>
       <c r="L45" t="inlineStr"/>
       <c r="M45" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>N om Ledningsmossen, Drängedalen, Vg</t>
+          <t>Långesjön, nordost om, Vg</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>343920</v>
+        <v>343939</v>
       </c>
       <c r="R45" t="n">
-        <v>6434211</v>
+        <v>6434333</v>
       </c>
       <c r="S45" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -6011,22 +5775,17 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2024-06-29</t>
-        </is>
-      </c>
-      <c r="Z45" t="inlineStr">
-        <is>
-          <t>11:35</t>
+          <t>2024-04-15</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2024-06-29</t>
-        </is>
-      </c>
-      <c r="AB45" t="inlineStr">
-        <is>
-          <t>11:35</t>
+          <t>2024-04-15</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>På ett torrträd av en gran. På bilden är det 9 mm mellan papperets linjer.</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -6035,76 +5794,73 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
+      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Ola Freijd</t>
+          <t>Thomas Grönlund</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Ola Freijd</t>
+          <t>Thomas Grönlund</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>118207885</v>
+        <v>119447428</v>
       </c>
       <c r="B46" t="n">
-        <v>57443</v>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5179</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>103021</v>
+        <v>100526</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr"/>
       <c r="K46" t="inlineStr"/>
       <c r="L46" t="inlineStr"/>
       <c r="M46" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Bergrygg 2 N Bredmossen, Drängedalen, Vg</t>
+          <t>Kant mot hygge NV Bredmossen, Drängedalen , Vg</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>344215</v>
+        <v>344144</v>
       </c>
       <c r="R46" t="n">
-        <v>6434430</v>
+        <v>6434438</v>
       </c>
       <c r="S46" t="n">
         <v>25</v>
@@ -6131,22 +5887,27 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2024-06-29</t>
+          <t>2024-08-12</t>
         </is>
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2024-06-29</t>
+          <t>2024-08-12</t>
         </is>
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Granlåga med massor av spår. Hjälp med artbestämning via Facebook-gruppen Långhorningar.</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6155,6 +5916,7 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
+      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
@@ -6173,15 +5935,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>118756024</v>
+        <v>118755601</v>
       </c>
       <c r="B47" t="n">
-        <v>57445</v>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5178</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6189,46 +5946,43 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>103021</v>
+        <v>102204</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Grönhjon</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Callidium aeneum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(De Geer, 1775)</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr"/>
       <c r="K47" t="inlineStr"/>
       <c r="L47" t="inlineStr"/>
       <c r="M47" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>N om Ledningsmossen, Drängedalen, Vg</t>
+          <t>Kjolgran N Ledningsmossen, Drängedalen, Vg</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>343920</v>
+        <v>343953</v>
       </c>
       <c r="R47" t="n">
-        <v>6434211</v>
+        <v>6434253</v>
       </c>
       <c r="S47" t="n">
         <v>25</v>
@@ -6260,7 +6014,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>07:45</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -6270,7 +6024,12 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>07:55</t>
+          <t>11:15</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Hjälp med artbestämning via Facebookgruppen Långhorningar.</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6279,6 +6038,7 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
+      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
@@ -6297,62 +6057,54 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>118756709</v>
+        <v>119447773</v>
       </c>
       <c r="B48" t="n">
-        <v>57150</v>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5178</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100100</v>
+        <v>102204</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Bivråk</t>
+          <t>Grönhjon</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Pernis apivorus</t>
+          <t>Callidium aeneum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(De Geer, 1775)</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr"/>
       <c r="K48" t="inlineStr"/>
       <c r="L48" t="inlineStr"/>
       <c r="M48" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Skog NO Ledningsmossen, Drängedalen, Vg</t>
+          <t>Kjolgran SO Långemossen, Drängedalen , Vg</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>343996</v>
+        <v>343964</v>
       </c>
       <c r="R48" t="n">
-        <v>6434225</v>
+        <v>6434348</v>
       </c>
       <c r="S48" t="n">
         <v>25</v>
@@ -6379,27 +6131,27 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2024-07-21</t>
+          <t>2024-08-12</t>
         </is>
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2024-07-21</t>
+          <t>2024-08-12</t>
         </is>
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>Rörde sig över Ledningsmossen, ropande.</t>
+          <t>Hjälp med artbestämning via Facebook-gruppen Långhorningar.</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6408,6 +6160,7 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
+      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
@@ -6426,58 +6179,54 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>118756857</v>
+        <v>120391898</v>
       </c>
       <c r="B49" t="n">
-        <v>56504</v>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5178</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100138</v>
+        <v>102204</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Grönhjon</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Callidium aeneum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(De Geer, 1775)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr"/>
       <c r="K49" t="inlineStr"/>
       <c r="L49" t="inlineStr"/>
       <c r="M49" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Häll 3 NV Bredmossen, Drängedalen, Vg</t>
+          <t>Kjolgran 6 Ö Ledningsmossen, Drängedalen, Vg</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>344067</v>
+        <v>344183</v>
       </c>
       <c r="R49" t="n">
-        <v>6434348</v>
+        <v>6434303</v>
       </c>
       <c r="S49" t="n">
         <v>25</v>
@@ -6504,22 +6253,22 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2024-07-21</t>
+          <t>2024-10-06</t>
         </is>
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2024-07-21</t>
+          <t>2024-10-06</t>
         </is>
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6528,6 +6277,7 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
+      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
@@ -6546,10 +6296,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>118755601</v>
+        <v>120391922</v>
       </c>
       <c r="B50" t="n">
-        <v>5176</v>
+        <v>5178</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6580,20 +6330,20 @@
       <c r="L50" t="inlineStr"/>
       <c r="M50" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Kjolgran N Ledningsmossen, Drängedalen, Vg</t>
+          <t>Kjolgran 7 Ö Ledningsmossen, Drängedalen, Vg</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>343953</v>
+        <v>344183</v>
       </c>
       <c r="R50" t="n">
-        <v>6434253</v>
+        <v>6434312</v>
       </c>
       <c r="S50" t="n">
         <v>25</v>
@@ -6620,27 +6370,22 @@
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2024-07-21</t>
+          <t>2024-10-06</t>
         </is>
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2024-07-21</t>
+          <t>2024-10-06</t>
         </is>
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>11:15</t>
-        </is>
-      </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>Hjälp med artbestämning via Facebookgruppen Långhorningar.</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6668,15 +6413,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>119447788</v>
+        <v>120391963</v>
       </c>
       <c r="B51" t="n">
-        <v>57326</v>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5178</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6684,42 +6424,43 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100049</v>
+        <v>102204</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grönhjon</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Callidium aeneum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(De Geer, 1775)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr"/>
       <c r="K51" t="inlineStr"/>
       <c r="L51" t="inlineStr"/>
       <c r="M51" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>S om Långemossen 3, Drängedalen, Vg</t>
+          <t>Kjolgran 8 Ö Ledningsmossen, Drängedalen, Vg</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>343963</v>
+        <v>344145</v>
       </c>
       <c r="R51" t="n">
-        <v>6434292</v>
+        <v>6434343</v>
       </c>
       <c r="S51" t="n">
         <v>25</v>
@@ -6746,27 +6487,22 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2024-08-12</t>
+          <t>2024-10-06</t>
         </is>
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2024-08-12</t>
+          <t>2024-10-06</t>
         </is>
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>15:05</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Spår efter födosök i torr granstubbe.</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6775,6 +6511,7 @@
       <c r="AE51" t="b">
         <v>0</v>
       </c>
+      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
@@ -6793,32 +6530,27 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>119447662</v>
+        <v>117137881</v>
       </c>
       <c r="B52" t="n">
-        <v>57326</v>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57144</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100049</v>
+        <v>102613</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -6831,20 +6563,20 @@
       <c r="L52" t="inlineStr"/>
       <c r="M52" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Kant mot hygge NV Bredmossen, Drängedalen , Vg</t>
+          <t>Häll 4 NO Ledningsmossen, Drängedalen, Vg</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>344144</v>
+        <v>344000</v>
       </c>
       <c r="R52" t="n">
-        <v>6434438</v>
+        <v>6434259</v>
       </c>
       <c r="S52" t="n">
         <v>25</v>
@@ -6871,27 +6603,22 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2024-08-12</t>
+          <t>2024-05-17</t>
         </is>
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2024-08-12</t>
+          <t>2024-05-17</t>
         </is>
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>12:05</t>
-        </is>
-      </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>Spår efter födosök i granstubbe.</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6918,15 +6645,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>119447428</v>
+        <v>117552948</v>
       </c>
       <c r="B53" t="n">
-        <v>5169</v>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57144</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6934,43 +6656,42 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100526</v>
+        <v>102613</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="J53" t="inlineStr"/>
       <c r="K53" t="inlineStr"/>
       <c r="L53" t="inlineStr"/>
       <c r="M53" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Kant mot hygge NV Bredmossen, Drängedalen , Vg</t>
+          <t>Norrkant Ledningsmossen, Drängedalen, Vg</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>344144</v>
+        <v>343871</v>
       </c>
       <c r="R53" t="n">
-        <v>6434438</v>
+        <v>6434192</v>
       </c>
       <c r="S53" t="n">
         <v>25</v>
@@ -6997,27 +6718,22 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2024-08-12</t>
+          <t>2024-05-29</t>
         </is>
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2024-08-12</t>
+          <t>2024-05-29</t>
         </is>
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>12:00</t>
-        </is>
-      </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>Granlåga med massor av spår. Hjälp med artbestämning via Facebook-gruppen Långhorningar.</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -7026,7 +6742,6 @@
       <c r="AE53" t="b">
         <v>0</v>
       </c>
-      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
@@ -7045,15 +6760,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>119447377</v>
+        <v>118756349</v>
       </c>
       <c r="B54" t="n">
-        <v>57463</v>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57794</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -7061,21 +6771,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>103021</v>
+        <v>102621</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Sparvuggla</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Glaucidium passerinum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -7087,20 +6797,20 @@
       <c r="L54" t="inlineStr"/>
       <c r="M54" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Bergrygg 3 N Bredmossen, Drängedalen, Vg</t>
+          <t>Skog 3 NO Ledningsmossen, Drängedalen, Vg</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>344227</v>
+        <v>343970</v>
       </c>
       <c r="R54" t="n">
-        <v>6434396</v>
+        <v>6434151</v>
       </c>
       <c r="S54" t="n">
         <v>25</v>
@@ -7127,22 +6837,22 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2024-08-12</t>
+          <t>2024-07-21</t>
         </is>
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>08:10</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2024-08-12</t>
+          <t>2024-07-21</t>
         </is>
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>08:10</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -7169,15 +6879,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>119447432</v>
+        <v>116012544</v>
       </c>
       <c r="B55" t="n">
-        <v>5189</v>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58327</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -7185,16 +6890,16 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>105930</v>
+        <v>103015</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -7202,29 +6907,32 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I55" t="inlineStr"/>
-      <c r="J55" t="inlineStr"/>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K55" t="inlineStr"/>
       <c r="L55" t="inlineStr"/>
       <c r="M55" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Kant mot hygge NV Bredmossen, Drängedalen , Vg</t>
+          <t>Långesjön, nordost om, Vg</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>344144</v>
+        <v>344262</v>
       </c>
       <c r="R55" t="n">
-        <v>6434438</v>
+        <v>6434376</v>
       </c>
       <c r="S55" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -7248,27 +6956,17 @@
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>2024-08-12</t>
-        </is>
-      </c>
-      <c r="Z55" t="inlineStr">
-        <is>
-          <t>12:00</t>
+          <t>2024-04-15</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2024-08-12</t>
-        </is>
-      </c>
-      <c r="AB55" t="inlineStr">
-        <is>
-          <t>12:00</t>
+          <t>2024-04-15</t>
         </is>
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>Granlåga med massor av spår. Hjälp med artbestämning via Facebook-gruppen Långhorningar.</t>
+          <t>I mossekanten</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -7277,77 +6975,71 @@
       <c r="AE55" t="b">
         <v>0</v>
       </c>
-      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Ola Freijd</t>
+          <t>Thomas Grönlund</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Ola Freijd</t>
+          <t>Thomas Grönlund</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>119446914</v>
+        <v>116013101</v>
       </c>
       <c r="B56" t="n">
-        <v>57463</v>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58327</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>103021</v>
+        <v>103015</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K56" t="inlineStr"/>
       <c r="L56" t="inlineStr"/>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+      <c r="M56" t="inlineStr"/>
       <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Sumpskog NV Bredmossen, NO kanten, Drängedalen, Vg</t>
+          <t>Långesjön, nordost om, Vg</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>344161</v>
+        <v>344211</v>
       </c>
       <c r="R56" t="n">
-        <v>6434293</v>
+        <v>6434479</v>
       </c>
       <c r="S56" t="n">
         <v>25</v>
@@ -7374,22 +7066,22 @@
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>2024-08-12</t>
+          <t>2024-04-15</t>
         </is>
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>07:25</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2024-08-12</t>
+          <t>2024-04-15</t>
         </is>
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>07:25</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7404,27 +7096,22 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Ola Freijd</t>
+          <t>Thomas Grönlund</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Ola Freijd</t>
+          <t>Thomas Grönlund</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>119447676</v>
+        <v>120419699</v>
       </c>
       <c r="B57" t="n">
-        <v>94321</v>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58327</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7432,41 +7119,49 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>2810</v>
+        <v>103015</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr"/>
-      <c r="J57" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K57" t="inlineStr"/>
       <c r="L57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Kant mot hygge NV Bredmossen, Drängedalen , Vg</t>
+          <t>Ledningsmossen, väster om, Vg</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>344144</v>
+        <v>343654</v>
       </c>
       <c r="R57" t="n">
-        <v>6434438</v>
+        <v>6434098</v>
       </c>
       <c r="S57" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -7490,27 +7185,22 @@
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>2024-08-12</t>
+          <t>2024-05-21</t>
         </is>
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2024-08-12</t>
+          <t>2024-05-21</t>
         </is>
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>12:15</t>
-        </is>
-      </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>Mycket.</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7519,34 +7209,28 @@
       <c r="AE57" t="b">
         <v>0</v>
       </c>
-      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Ola Freijd</t>
+          <t>Lars Gerre</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Ola Freijd</t>
+          <t>Lars Gerre</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>119447229</v>
+        <v>118207885</v>
       </c>
       <c r="B58" t="n">
-        <v>57463</v>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7571,29 +7255,25 @@
           <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I58" t="inlineStr"/>
       <c r="K58" t="inlineStr"/>
       <c r="L58" t="inlineStr"/>
       <c r="M58" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Bergrygg N Bredmossen, Drängedalen, Vg</t>
+          <t>Bergrygg 2 N Bredmossen, Drängedalen, Vg</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>344254</v>
+        <v>344215</v>
       </c>
       <c r="R58" t="n">
-        <v>6434389</v>
+        <v>6434430</v>
       </c>
       <c r="S58" t="n">
         <v>25</v>
@@ -7620,22 +7300,22 @@
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>2024-08-12</t>
+          <t>2024-06-29</t>
         </is>
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2024-08-12</t>
+          <t>2024-06-29</t>
         </is>
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7662,15 +7342,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>119447415</v>
+        <v>118756005</v>
       </c>
       <c r="B59" t="n">
-        <v>57326</v>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7678,42 +7353,46 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K59" t="inlineStr"/>
       <c r="L59" t="inlineStr"/>
       <c r="M59" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Skog 150 m NNV Bredmossen, Vg</t>
+          <t>Skog 3 NO Ledningsmossen, Drängedalen, Vg</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>344191</v>
+        <v>343970</v>
       </c>
       <c r="R59" t="n">
-        <v>6434464</v>
+        <v>6434151</v>
       </c>
       <c r="S59" t="n">
         <v>25</v>
@@ -7740,27 +7419,22 @@
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>2024-08-12</t>
+          <t>2024-07-21</t>
         </is>
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>07:35</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2024-08-12</t>
+          <t>2024-07-21</t>
         </is>
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>11:40</t>
-        </is>
-      </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>Spår efter födosök i granstam.</t>
+          <t>07:35</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7787,15 +7461,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>120392393</v>
+        <v>118756024</v>
       </c>
       <c r="B60" t="n">
-        <v>57488</v>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7820,25 +7489,29 @@
           <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
-      <c r="I60" t="inlineStr"/>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K60" t="inlineStr"/>
       <c r="L60" t="inlineStr"/>
       <c r="M60" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Skog 2 NV Bredmossen, Drängedalen , Vg</t>
+          <t>N om Ledningsmossen, Drängedalen, Vg</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>344222</v>
+        <v>343920</v>
       </c>
       <c r="R60" t="n">
-        <v>6434363</v>
+        <v>6434211</v>
       </c>
       <c r="S60" t="n">
         <v>25</v>
@@ -7865,22 +7538,22 @@
       </c>
       <c r="Y60" t="inlineStr">
         <is>
-          <t>2024-10-06</t>
+          <t>2024-07-21</t>
         </is>
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>07:45</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>2024-10-06</t>
+          <t>2024-07-21</t>
         </is>
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>07:55</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7907,10 +7580,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>120391963</v>
+        <v>119446914</v>
       </c>
       <c r="B61" t="n">
-        <v>5176</v>
+        <v>58114</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7918,43 +7591,42 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>102204</v>
+        <v>103021</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Grönhjon</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Callidium aeneum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(De Geer, 1775)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
-      <c r="J61" t="inlineStr"/>
       <c r="K61" t="inlineStr"/>
       <c r="L61" t="inlineStr"/>
       <c r="M61" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Kjolgran 8 Ö Ledningsmossen, Drängedalen, Vg</t>
+          <t>Sumpskog NV Bredmossen, NO kanten, Drängedalen, Vg</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>344145</v>
+        <v>344161</v>
       </c>
       <c r="R61" t="n">
-        <v>6434343</v>
+        <v>6434293</v>
       </c>
       <c r="S61" t="n">
         <v>25</v>
@@ -7981,22 +7653,22 @@
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>2024-10-06</t>
+          <t>2024-08-12</t>
         </is>
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>07:25</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2024-10-06</t>
+          <t>2024-08-12</t>
         </is>
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>07:25</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -8005,7 +7677,6 @@
       <c r="AE61" t="b">
         <v>0</v>
       </c>
-      <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="b">
         <v>0</v>
       </c>
@@ -8024,62 +7695,60 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>120408193</v>
+        <v>119447229</v>
       </c>
       <c r="B62" t="n">
-        <v>5189</v>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>105930</v>
+        <v>103021</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr"/>
-      <c r="J62" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K62" t="inlineStr"/>
       <c r="L62" t="inlineStr"/>
       <c r="M62" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Bredmossen, Vg</t>
+          <t>Bergrygg N Bredmossen, Drängedalen, Vg</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>344249</v>
+        <v>344254</v>
       </c>
       <c r="R62" t="n">
-        <v>6434428</v>
+        <v>6434389</v>
       </c>
       <c r="S62" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -8103,17 +7772,22 @@
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>2024-05-21</t>
+          <t>2024-08-12</t>
+        </is>
+      </c>
+      <c r="Z62" t="inlineStr">
+        <is>
+          <t>09:15</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2024-05-21</t>
-        </is>
-      </c>
-      <c r="AC62" t="inlineStr">
-        <is>
-          <t>I död gran.</t>
+          <t>2024-08-12</t>
+        </is>
+      </c>
+      <c r="AB62" t="inlineStr">
+        <is>
+          <t>09:15</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -8122,34 +7796,28 @@
       <c r="AE62" t="b">
         <v>0</v>
       </c>
-      <c r="AF62" t="inlineStr"/>
       <c r="AG62" t="b">
         <v>0</v>
       </c>
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Lars Gerre</t>
+          <t>Ola Freijd</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Lars Gerre</t>
+          <t>Ola Freijd</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>120392432</v>
+        <v>119447332</v>
       </c>
       <c r="B63" t="n">
-        <v>57488</v>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -8174,25 +7842,29 @@
           <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
-      <c r="I63" t="inlineStr"/>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="K63" t="inlineStr"/>
       <c r="L63" t="inlineStr"/>
       <c r="M63" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Skog SO Trehörningen, Drängedalen, Vg</t>
+          <t>Bergrygg 3 N Bredmossen, Drängedalen, Vg</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>343589</v>
+        <v>344227</v>
       </c>
       <c r="R63" t="n">
-        <v>6434074</v>
+        <v>6434396</v>
       </c>
       <c r="S63" t="n">
         <v>25</v>
@@ -8219,22 +7891,27 @@
       </c>
       <c r="Y63" t="inlineStr">
         <is>
-          <t>2024-10-06</t>
+          <t>2024-08-12</t>
         </is>
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>2024-10-06</t>
+          <t>2024-08-12</t>
         </is>
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>10:25</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>Minst 4 ex. En sedd, övriga lockläten runt omkring.</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -8261,15 +7938,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>120408243</v>
+        <v>120392393</v>
       </c>
       <c r="B64" t="n">
-        <v>57351</v>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -8277,21 +7949,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -8299,23 +7971,23 @@
       <c r="L64" t="inlineStr"/>
       <c r="M64" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Bredmossen, Vg</t>
+          <t>Skog 2 NV Bredmossen, Drängedalen , Vg</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>344249</v>
+        <v>344222</v>
       </c>
       <c r="R64" t="n">
-        <v>6434428</v>
+        <v>6434363</v>
       </c>
       <c r="S64" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -8339,17 +8011,22 @@
       </c>
       <c r="Y64" t="inlineStr">
         <is>
-          <t>2024-05-21</t>
+          <t>2024-10-06</t>
+        </is>
+      </c>
+      <c r="Z64" t="inlineStr">
+        <is>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>2024-05-21</t>
-        </is>
-      </c>
-      <c r="AC64" t="inlineStr">
-        <is>
-          <t>Ganska färska hack, vid basen av död gran.</t>
+          <t>2024-10-06</t>
+        </is>
+      </c>
+      <c r="AB64" t="inlineStr">
+        <is>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -8364,22 +8041,22 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Lars Gerre</t>
+          <t>Ola Freijd</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Lars Gerre</t>
+          <t>Ola Freijd</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>120391922</v>
+        <v>120392432</v>
       </c>
       <c r="B65" t="n">
-        <v>5176</v>
+        <v>58114</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8387,43 +8064,42 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>102204</v>
+        <v>103021</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Grönhjon</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Callidium aeneum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(De Geer, 1775)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
-      <c r="J65" t="inlineStr"/>
       <c r="K65" t="inlineStr"/>
       <c r="L65" t="inlineStr"/>
       <c r="M65" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Kjolgran 7 Ö Ledningsmossen, Drängedalen, Vg</t>
+          <t>Skog SO Trehörningen, Drängedalen, Vg</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>344183</v>
+        <v>343589</v>
       </c>
       <c r="R65" t="n">
-        <v>6434312</v>
+        <v>6434074</v>
       </c>
       <c r="S65" t="n">
         <v>25</v>
@@ -8455,7 +8131,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -8465,7 +8141,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -8474,7 +8150,6 @@
       <c r="AE65" t="b">
         <v>0</v>
       </c>
-      <c r="AF65" t="inlineStr"/>
       <c r="AG65" t="b">
         <v>0</v>
       </c>
@@ -8493,61 +8168,60 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>120408289</v>
+        <v>120419416</v>
       </c>
       <c r="B66" t="n">
-        <v>58011</v>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>103044</v>
+        <v>103021</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K66" t="inlineStr"/>
       <c r="L66" t="inlineStr"/>
       <c r="M66" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Bredmossen, Vg</t>
+          <t>Bredmossen, nordväst om, Vg</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>344249</v>
+        <v>344070</v>
       </c>
       <c r="R66" t="n">
-        <v>6434428</v>
+        <v>6434330</v>
       </c>
       <c r="S66" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -8576,7 +8250,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -8587,6 +8261,11 @@
       <c r="AB66" t="inlineStr">
         <is>
           <t>18:00</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>I kanten av sumpskog.</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8613,10 +8292,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>120391898</v>
+        <v>123819731</v>
       </c>
       <c r="B67" t="n">
-        <v>5176</v>
+        <v>58114</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8624,43 +8303,42 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>102204</v>
+        <v>103021</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Grönhjon</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Callidium aeneum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(De Geer, 1775)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
-      <c r="J67" t="inlineStr"/>
       <c r="K67" t="inlineStr"/>
       <c r="L67" t="inlineStr"/>
       <c r="M67" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Kjolgran 6 Ö Ledningsmossen, Drängedalen, Vg</t>
+          <t>Skog 4 NV Bredmossen, Drängedalen, Vg</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>344183</v>
+        <v>344218</v>
       </c>
       <c r="R67" t="n">
-        <v>6434303</v>
+        <v>6434327</v>
       </c>
       <c r="S67" t="n">
         <v>25</v>
@@ -8687,22 +8365,22 @@
       </c>
       <c r="Y67" t="inlineStr">
         <is>
-          <t>2024-10-06</t>
+          <t>2025-03-09</t>
         </is>
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>2024-10-06</t>
+          <t>2025-03-09</t>
         </is>
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8711,7 +8389,6 @@
       <c r="AE67" t="b">
         <v>0</v>
       </c>
-      <c r="AF67" t="inlineStr"/>
       <c r="AG67" t="b">
         <v>0</v>
       </c>
@@ -8730,15 +8407,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>120419793</v>
+        <v>116021691</v>
       </c>
       <c r="B68" t="n">
-        <v>96281</v>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58636</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8746,41 +8418,49 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>2569</v>
+        <v>103044</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr"/>
-      <c r="J68" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="K68" t="inlineStr"/>
       <c r="L68" t="inlineStr"/>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
       <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Trehörningen, sydost om, Vg</t>
+          <t>Långesjön, nordost om, Vg</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>343605</v>
+        <v>344243</v>
       </c>
       <c r="R68" t="n">
-        <v>6434107</v>
+        <v>6434390</v>
       </c>
       <c r="S68" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -8804,17 +8484,17 @@
       </c>
       <c r="Y68" t="inlineStr">
         <is>
-          <t>2024-05-21</t>
+          <t>2024-04-15</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>2024-05-21</t>
+          <t>2024-04-15</t>
         </is>
       </c>
       <c r="AC68" t="inlineStr">
         <is>
-          <t>Några större tuvor.</t>
+          <t>Hörde en handfull grönsiskor över mig i trädhöjd när jag kollade kantvitmossan.</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8823,34 +8503,28 @@
       <c r="AE68" t="b">
         <v>0</v>
       </c>
-      <c r="AF68" t="inlineStr"/>
       <c r="AG68" t="b">
         <v>0</v>
       </c>
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Lars Gerre</t>
+          <t>Thomas Grönlund</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Lars Gerre</t>
+          <t>Thomas Grönlund</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>120419699</v>
+        <v>120408289</v>
       </c>
       <c r="B69" t="n">
-        <v>57704</v>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58636</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8858,16 +8532,16 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>103015</v>
+        <v>103044</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -8875,29 +8549,25 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I69" t="inlineStr"/>
       <c r="K69" t="inlineStr"/>
       <c r="L69" t="inlineStr"/>
       <c r="M69" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Ledningsmossen, väster om, Vg</t>
+          <t>Bredmossen, Vg</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>343654</v>
+        <v>344249</v>
       </c>
       <c r="R69" t="n">
-        <v>6434098</v>
+        <v>6434428</v>
       </c>
       <c r="S69" t="n">
         <v>5</v>
@@ -8929,17 +8599,17 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>2024-05-21</t>
+        </is>
+      </c>
+      <c r="AB69" t="inlineStr">
+        <is>
           <t>18:00</t>
-        </is>
-      </c>
-      <c r="AA69" t="inlineStr">
-        <is>
-          <t>2024-05-21</t>
-        </is>
-      </c>
-      <c r="AB69" t="inlineStr">
-        <is>
-          <t>18:30</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8966,65 +8636,56 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>120419416</v>
+        <v>123819735</v>
       </c>
       <c r="B70" t="n">
-        <v>57488</v>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58636</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>103021</v>
+        <v>103044</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
       <c r="K70" t="inlineStr"/>
       <c r="L70" t="inlineStr"/>
       <c r="M70" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Bredmossen, nordväst om, Vg</t>
+          <t>Skog 2 NV Bredmossen, Drängedalen , Vg</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>344070</v>
+        <v>344222</v>
       </c>
       <c r="R70" t="n">
-        <v>6434330</v>
+        <v>6434363</v>
       </c>
       <c r="S70" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -9048,27 +8709,27 @@
       </c>
       <c r="Y70" t="inlineStr">
         <is>
-          <t>2024-05-21</t>
+          <t>2025-03-09</t>
         </is>
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>2024-05-21</t>
+          <t>2025-03-09</t>
         </is>
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AC70" t="inlineStr">
         <is>
-          <t>I kanten av sumpskog.</t>
+          <t>Flera stycken, minst en sjöng.</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -9083,27 +8744,22 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Lars Gerre</t>
+          <t>Ola Freijd</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Lars Gerre</t>
+          <t>Ola Freijd</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>120419661</v>
+        <v>116012504</v>
       </c>
       <c r="B71" t="n">
-        <v>5189</v>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5199</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -9140,14 +8796,14 @@
       <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Ledningsmossen, väster om, Vg</t>
+          <t>Långesjön, nordost om, Vg</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>343654</v>
+        <v>344262</v>
       </c>
       <c r="R71" t="n">
-        <v>6434098</v>
+        <v>6434376</v>
       </c>
       <c r="S71" t="n">
         <v>5</v>
@@ -9174,17 +8830,17 @@
       </c>
       <c r="Y71" t="inlineStr">
         <is>
-          <t>2024-05-21</t>
+          <t>2024-04-15</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>2024-05-21</t>
+          <t>2024-04-15</t>
         </is>
       </c>
       <c r="AC71" t="inlineStr">
         <is>
-          <t>I död gran,</t>
+          <t>Noterade gnagspår på senvuxen klen, tvåtoppig gran i mossekanten</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -9200,27 +8856,22 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Lars Gerre</t>
+          <t>Thomas Grönlund</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Lars Gerre</t>
+          <t>Thomas Grönlund</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>123819752</v>
+        <v>116018293</v>
       </c>
       <c r="B72" t="n">
-        <v>56722</v>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5199</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -9228,45 +8879,46 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>100138</v>
+        <v>105930</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
+      <c r="J72" t="inlineStr"/>
       <c r="K72" t="inlineStr"/>
       <c r="L72" t="inlineStr"/>
       <c r="M72" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Häll 4 NO Ledningsmossen, Drängedalen, Vg</t>
+          <t>Långesjön, nordost om, Vg</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>344000</v>
+        <v>343939</v>
       </c>
       <c r="R72" t="n">
-        <v>6434259</v>
+        <v>6434333</v>
       </c>
       <c r="S72" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -9290,22 +8942,27 @@
       </c>
       <c r="Y72" t="inlineStr">
         <is>
-          <t>2025-03-09</t>
+          <t>2024-04-15</t>
         </is>
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
         <is>
-          <t>2025-03-09</t>
+          <t>2024-04-15</t>
         </is>
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AC72" t="inlineStr">
+        <is>
+          <t>Spår på ett torrträd av en gran.</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -9314,33 +8971,29 @@
       <c r="AE72" t="b">
         <v>0</v>
       </c>
+      <c r="AF72" t="inlineStr"/>
       <c r="AG72" t="b">
         <v>0</v>
       </c>
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Ola Freijd</t>
+          <t>Thomas Grönlund</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Ola Freijd</t>
+          <t>Thomas Grönlund</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>123819735</v>
+        <v>116018500</v>
       </c>
       <c r="B73" t="n">
-        <v>58191</v>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5199</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -9348,16 +9001,16 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>103044</v>
+        <v>105930</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -9366,27 +9019,28 @@
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
+      <c r="J73" t="inlineStr"/>
       <c r="K73" t="inlineStr"/>
       <c r="L73" t="inlineStr"/>
       <c r="M73" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Skog 2 NV Bredmossen, Drängedalen , Vg</t>
+          <t>Långesjön, nordost om, Vg</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>344222</v>
+        <v>343917</v>
       </c>
       <c r="R73" t="n">
-        <v>6434363</v>
+        <v>6434318</v>
       </c>
       <c r="S73" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -9410,27 +9064,27 @@
       </c>
       <c r="Y73" t="inlineStr">
         <is>
-          <t>2025-03-09</t>
+          <t>2024-04-15</t>
         </is>
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>2025-03-09</t>
+          <t>2024-04-15</t>
         </is>
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AC73" t="inlineStr">
         <is>
-          <t>Flera stycken, minst en sjöng.</t>
+          <t>Spår på ett torrträd av en 15 cm tjock gran.</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -9439,21 +9093,2286 @@
       <c r="AE73" t="b">
         <v>0</v>
       </c>
+      <c r="AF73" t="inlineStr"/>
       <c r="AG73" t="b">
         <v>0</v>
       </c>
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
+          <t>Thomas Grönlund</t>
+        </is>
+      </c>
+      <c r="AX73" t="inlineStr">
+        <is>
+          <t>Thomas Grönlund</t>
+        </is>
+      </c>
+      <c r="AY73" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>116018541</v>
+      </c>
+      <c r="B74" t="n">
+        <v>5199</v>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>105930</v>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Vågbandad barkbock</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Semanotus undatus</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
+      <c r="J74" t="inlineStr"/>
+      <c r="K74" t="inlineStr"/>
+      <c r="L74" t="inlineStr"/>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N74" t="inlineStr"/>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>Långesjön, nordost om, Vg</t>
+        </is>
+      </c>
+      <c r="Q74" t="n">
+        <v>343925</v>
+      </c>
+      <c r="R74" t="n">
+        <v>6434320</v>
+      </c>
+      <c r="S74" t="n">
+        <v>5</v>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W74" t="inlineStr">
+        <is>
+          <t>Hålanda</t>
+        </is>
+      </c>
+      <c r="Y74" t="inlineStr">
+        <is>
+          <t>2024-04-15</t>
+        </is>
+      </c>
+      <c r="Z74" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>2024-04-15</t>
+        </is>
+      </c>
+      <c r="AB74" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AC74" t="inlineStr">
+        <is>
+          <t>Spår på en gran i sumpskogen norr om bäcken.</t>
+        </is>
+      </c>
+      <c r="AD74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF74" t="inlineStr"/>
+      <c r="AG74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT74" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>Thomas Grönlund</t>
+        </is>
+      </c>
+      <c r="AX74" t="inlineStr">
+        <is>
+          <t>Thomas Grönlund</t>
+        </is>
+      </c>
+      <c r="AY74" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>116018621</v>
+      </c>
+      <c r="B75" t="n">
+        <v>5199</v>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>105930</v>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Vågbandad barkbock</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Semanotus undatus</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr"/>
+      <c r="J75" t="inlineStr"/>
+      <c r="K75" t="inlineStr"/>
+      <c r="L75" t="inlineStr"/>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N75" t="inlineStr"/>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>Långesjön, norr om, Vg</t>
+        </is>
+      </c>
+      <c r="Q75" t="n">
+        <v>343562</v>
+      </c>
+      <c r="R75" t="n">
+        <v>6434089</v>
+      </c>
+      <c r="S75" t="n">
+        <v>5</v>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W75" t="inlineStr">
+        <is>
+          <t>Hålanda</t>
+        </is>
+      </c>
+      <c r="Y75" t="inlineStr">
+        <is>
+          <t>2024-04-15</t>
+        </is>
+      </c>
+      <c r="Z75" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AA75" t="inlineStr">
+        <is>
+          <t>2024-04-15</t>
+        </is>
+      </c>
+      <c r="AB75" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AC75" t="inlineStr">
+        <is>
+          <t>Spår på ett 15 cm tjockt torrträd av gran som stod i kanten av våtmarken.</t>
+        </is>
+      </c>
+      <c r="AD75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF75" t="inlineStr"/>
+      <c r="AG75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT75" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>Thomas Grönlund</t>
+        </is>
+      </c>
+      <c r="AX75" t="inlineStr">
+        <is>
+          <t>Thomas Grönlund</t>
+        </is>
+      </c>
+      <c r="AY75" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>116021091</v>
+      </c>
+      <c r="B76" t="n">
+        <v>5199</v>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>105930</v>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Vågbandad barkbock</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Semanotus undatus</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr"/>
+      <c r="J76" t="inlineStr"/>
+      <c r="K76" t="inlineStr"/>
+      <c r="L76" t="inlineStr"/>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N76" t="inlineStr"/>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>Långesjön, nordost om, Vg</t>
+        </is>
+      </c>
+      <c r="Q76" t="n">
+        <v>343941</v>
+      </c>
+      <c r="R76" t="n">
+        <v>6434219</v>
+      </c>
+      <c r="S76" t="n">
+        <v>5</v>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W76" t="inlineStr">
+        <is>
+          <t>Hålanda</t>
+        </is>
+      </c>
+      <c r="Y76" t="inlineStr">
+        <is>
+          <t>2024-04-15</t>
+        </is>
+      </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>2024-04-15</t>
+        </is>
+      </c>
+      <c r="AD76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF76" t="inlineStr"/>
+      <c r="AG76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT76" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>Thomas Grönlund</t>
+        </is>
+      </c>
+      <c r="AX76" t="inlineStr">
+        <is>
+          <t>Thomas Grönlund</t>
+        </is>
+      </c>
+      <c r="AY76" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>119447432</v>
+      </c>
+      <c r="B77" t="n">
+        <v>5199</v>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>105930</v>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Vågbandad barkbock</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Semanotus undatus</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr"/>
+      <c r="J77" t="inlineStr"/>
+      <c r="K77" t="inlineStr"/>
+      <c r="L77" t="inlineStr"/>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N77" t="inlineStr"/>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>Kant mot hygge NV Bredmossen, Drängedalen , Vg</t>
+        </is>
+      </c>
+      <c r="Q77" t="n">
+        <v>344144</v>
+      </c>
+      <c r="R77" t="n">
+        <v>6434438</v>
+      </c>
+      <c r="S77" t="n">
+        <v>25</v>
+      </c>
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V77" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W77" t="inlineStr">
+        <is>
+          <t>Hålanda</t>
+        </is>
+      </c>
+      <c r="Y77" t="inlineStr">
+        <is>
+          <t>2024-08-12</t>
+        </is>
+      </c>
+      <c r="Z77" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AA77" t="inlineStr">
+        <is>
+          <t>2024-08-12</t>
+        </is>
+      </c>
+      <c r="AB77" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AC77" t="inlineStr">
+        <is>
+          <t>Granlåga med massor av spår. Hjälp med artbestämning via Facebook-gruppen Långhorningar.</t>
+        </is>
+      </c>
+      <c r="AD77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF77" t="inlineStr"/>
+      <c r="AG77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT77" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
           <t>Ola Freijd</t>
         </is>
       </c>
-      <c r="AX73" t="inlineStr">
+      <c r="AX77" t="inlineStr">
         <is>
           <t>Ola Freijd</t>
         </is>
       </c>
-      <c r="AY73" t="inlineStr"/>
+      <c r="AY77" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>120408193</v>
+      </c>
+      <c r="B78" t="n">
+        <v>5199</v>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>105930</v>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Vågbandad barkbock</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Semanotus undatus</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr"/>
+      <c r="J78" t="inlineStr"/>
+      <c r="K78" t="inlineStr"/>
+      <c r="L78" t="inlineStr"/>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N78" t="inlineStr"/>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>Bredmossen, Vg</t>
+        </is>
+      </c>
+      <c r="Q78" t="n">
+        <v>344249</v>
+      </c>
+      <c r="R78" t="n">
+        <v>6434428</v>
+      </c>
+      <c r="S78" t="n">
+        <v>5</v>
+      </c>
+      <c r="T78" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V78" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W78" t="inlineStr">
+        <is>
+          <t>Hålanda</t>
+        </is>
+      </c>
+      <c r="Y78" t="inlineStr">
+        <is>
+          <t>2024-05-21</t>
+        </is>
+      </c>
+      <c r="AA78" t="inlineStr">
+        <is>
+          <t>2024-05-21</t>
+        </is>
+      </c>
+      <c r="AC78" t="inlineStr">
+        <is>
+          <t>I död gran.</t>
+        </is>
+      </c>
+      <c r="AD78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF78" t="inlineStr"/>
+      <c r="AG78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT78" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>Lars Gerre</t>
+        </is>
+      </c>
+      <c r="AX78" t="inlineStr">
+        <is>
+          <t>Lars Gerre</t>
+        </is>
+      </c>
+      <c r="AY78" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>120419661</v>
+      </c>
+      <c r="B79" t="n">
+        <v>5199</v>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>105930</v>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Vågbandad barkbock</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Semanotus undatus</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr"/>
+      <c r="J79" t="inlineStr"/>
+      <c r="K79" t="inlineStr"/>
+      <c r="L79" t="inlineStr"/>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N79" t="inlineStr"/>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>Ledningsmossen, väster om, Vg</t>
+        </is>
+      </c>
+      <c r="Q79" t="n">
+        <v>343654</v>
+      </c>
+      <c r="R79" t="n">
+        <v>6434098</v>
+      </c>
+      <c r="S79" t="n">
+        <v>5</v>
+      </c>
+      <c r="T79" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V79" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W79" t="inlineStr">
+        <is>
+          <t>Hålanda</t>
+        </is>
+      </c>
+      <c r="Y79" t="inlineStr">
+        <is>
+          <t>2024-05-21</t>
+        </is>
+      </c>
+      <c r="AA79" t="inlineStr">
+        <is>
+          <t>2024-05-21</t>
+        </is>
+      </c>
+      <c r="AC79" t="inlineStr">
+        <is>
+          <t>I död gran,</t>
+        </is>
+      </c>
+      <c r="AD79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF79" t="inlineStr"/>
+      <c r="AG79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT79" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>Lars Gerre</t>
+        </is>
+      </c>
+      <c r="AX79" t="inlineStr">
+        <is>
+          <t>Lars Gerre</t>
+        </is>
+      </c>
+      <c r="AY79" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>115941784</v>
+      </c>
+      <c r="B80" t="n">
+        <v>8444</v>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E80" t="n">
+        <v>106554</v>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Björksplintborre</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>Scolytus ratzeburgii</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr"/>
+      <c r="J80" t="inlineStr"/>
+      <c r="K80" t="inlineStr"/>
+      <c r="L80" t="inlineStr"/>
+      <c r="M80" t="inlineStr"/>
+      <c r="N80" t="inlineStr"/>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>Långesjön, norr om, Vg</t>
+        </is>
+      </c>
+      <c r="Q80" t="n">
+        <v>344002</v>
+      </c>
+      <c r="R80" t="n">
+        <v>6434216</v>
+      </c>
+      <c r="S80" t="n">
+        <v>5</v>
+      </c>
+      <c r="T80" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U80" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V80" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W80" t="inlineStr">
+        <is>
+          <t>Hålanda</t>
+        </is>
+      </c>
+      <c r="Y80" t="inlineStr">
+        <is>
+          <t>2024-03-26</t>
+        </is>
+      </c>
+      <c r="AA80" t="inlineStr">
+        <is>
+          <t>2024-03-26</t>
+        </is>
+      </c>
+      <c r="AC80" t="inlineStr">
+        <is>
+          <t>Noterade flera rader med hål från björksplintborre på en björkhögstubbe.</t>
+        </is>
+      </c>
+      <c r="AD80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF80" t="inlineStr"/>
+      <c r="AG80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT80" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>Thomas Grönlund</t>
+        </is>
+      </c>
+      <c r="AX80" t="inlineStr">
+        <is>
+          <t>Thomas Grönlund</t>
+        </is>
+      </c>
+      <c r="AY80" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>116015266</v>
+      </c>
+      <c r="B81" t="n">
+        <v>8444</v>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>106554</v>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Björksplintborre</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Scolytus ratzeburgii</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr"/>
+      <c r="J81" t="inlineStr"/>
+      <c r="K81" t="inlineStr"/>
+      <c r="L81" t="inlineStr"/>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N81" t="inlineStr"/>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>Långesjön, nordost om, Vg</t>
+        </is>
+      </c>
+      <c r="Q81" t="n">
+        <v>344160</v>
+      </c>
+      <c r="R81" t="n">
+        <v>6434320</v>
+      </c>
+      <c r="S81" t="n">
+        <v>5</v>
+      </c>
+      <c r="T81" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V81" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W81" t="inlineStr">
+        <is>
+          <t>Hålanda</t>
+        </is>
+      </c>
+      <c r="Y81" t="inlineStr">
+        <is>
+          <t>2024-04-15</t>
+        </is>
+      </c>
+      <c r="Z81" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="AA81" t="inlineStr">
+        <is>
+          <t>2024-04-15</t>
+        </is>
+      </c>
+      <c r="AB81" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="AC81" t="inlineStr">
+        <is>
+          <t>Rader med hål i en 2 m hög björkhögstubbe, i kanten på ett blötare parti.</t>
+        </is>
+      </c>
+      <c r="AD81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF81" t="inlineStr"/>
+      <c r="AG81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT81" t="inlineStr"/>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>Thomas Grönlund</t>
+        </is>
+      </c>
+      <c r="AX81" t="inlineStr">
+        <is>
+          <t>Thomas Grönlund</t>
+        </is>
+      </c>
+      <c r="AY81" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>116015307</v>
+      </c>
+      <c r="B82" t="n">
+        <v>8444</v>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E82" t="n">
+        <v>106554</v>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Björksplintborre</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>Scolytus ratzeburgii</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr"/>
+      <c r="J82" t="inlineStr"/>
+      <c r="K82" t="inlineStr"/>
+      <c r="L82" t="inlineStr"/>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N82" t="inlineStr"/>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>Långesjön, nordost om, Vg</t>
+        </is>
+      </c>
+      <c r="Q82" t="n">
+        <v>344154</v>
+      </c>
+      <c r="R82" t="n">
+        <v>6434302</v>
+      </c>
+      <c r="S82" t="n">
+        <v>5</v>
+      </c>
+      <c r="T82" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U82" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V82" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W82" t="inlineStr">
+        <is>
+          <t>Hålanda</t>
+        </is>
+      </c>
+      <c r="Y82" t="inlineStr">
+        <is>
+          <t>2024-04-15</t>
+        </is>
+      </c>
+      <c r="Z82" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="AA82" t="inlineStr">
+        <is>
+          <t>2024-04-15</t>
+        </is>
+      </c>
+      <c r="AB82" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="AC82" t="inlineStr">
+        <is>
+          <t>Rader med hål efter björksplintborren i en 3 m hög björkhögstubbe i sumpskogen.</t>
+        </is>
+      </c>
+      <c r="AD82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF82" t="inlineStr"/>
+      <c r="AG82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT82" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>Thomas Grönlund</t>
+        </is>
+      </c>
+      <c r="AX82" t="inlineStr">
+        <is>
+          <t>Thomas Grönlund</t>
+        </is>
+      </c>
+      <c r="AY82" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>116015428</v>
+      </c>
+      <c r="B83" t="n">
+        <v>8444</v>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E83" t="n">
+        <v>106554</v>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Björksplintborre</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>Scolytus ratzeburgii</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr"/>
+      <c r="J83" t="inlineStr"/>
+      <c r="K83" t="inlineStr"/>
+      <c r="L83" t="inlineStr"/>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N83" t="inlineStr"/>
+      <c r="P83" t="inlineStr">
+        <is>
+          <t>Långesjön, nordost om, Vg</t>
+        </is>
+      </c>
+      <c r="Q83" t="n">
+        <v>344140</v>
+      </c>
+      <c r="R83" t="n">
+        <v>6434310</v>
+      </c>
+      <c r="S83" t="n">
+        <v>5</v>
+      </c>
+      <c r="T83" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U83" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V83" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W83" t="inlineStr">
+        <is>
+          <t>Hålanda</t>
+        </is>
+      </c>
+      <c r="Y83" t="inlineStr">
+        <is>
+          <t>2024-04-15</t>
+        </is>
+      </c>
+      <c r="Z83" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AA83" t="inlineStr">
+        <is>
+          <t>2024-04-15</t>
+        </is>
+      </c>
+      <c r="AB83" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AC83" t="inlineStr">
+        <is>
+          <t>Rader med hål efter björksplintborren i en 5 m hög björkhögstubbe.</t>
+        </is>
+      </c>
+      <c r="AD83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF83" t="inlineStr"/>
+      <c r="AG83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT83" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>Thomas Grönlund</t>
+        </is>
+      </c>
+      <c r="AX83" t="inlineStr">
+        <is>
+          <t>Thomas Grönlund</t>
+        </is>
+      </c>
+      <c r="AY83" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>116015501</v>
+      </c>
+      <c r="B84" t="n">
+        <v>8444</v>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E84" t="n">
+        <v>106554</v>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Björksplintborre</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>Scolytus ratzeburgii</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr"/>
+      <c r="J84" t="inlineStr"/>
+      <c r="K84" t="inlineStr"/>
+      <c r="L84" t="inlineStr"/>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N84" t="inlineStr"/>
+      <c r="P84" t="inlineStr">
+        <is>
+          <t>Långesjön, nordost om, Vg</t>
+        </is>
+      </c>
+      <c r="Q84" t="n">
+        <v>344147</v>
+      </c>
+      <c r="R84" t="n">
+        <v>6434279</v>
+      </c>
+      <c r="S84" t="n">
+        <v>5</v>
+      </c>
+      <c r="T84" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U84" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V84" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W84" t="inlineStr">
+        <is>
+          <t>Hålanda</t>
+        </is>
+      </c>
+      <c r="Y84" t="inlineStr">
+        <is>
+          <t>2024-04-15</t>
+        </is>
+      </c>
+      <c r="Z84" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AA84" t="inlineStr">
+        <is>
+          <t>2024-04-15</t>
+        </is>
+      </c>
+      <c r="AB84" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AC84" t="inlineStr">
+        <is>
+          <t>Rader med hål efter björksplintborren i en 6 m hög björkhögstubbe.</t>
+        </is>
+      </c>
+      <c r="AD84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF84" t="inlineStr"/>
+      <c r="AG84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT84" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>Thomas Grönlund</t>
+        </is>
+      </c>
+      <c r="AX84" t="inlineStr">
+        <is>
+          <t>Thomas Grönlund</t>
+        </is>
+      </c>
+      <c r="AY84" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>116015532</v>
+      </c>
+      <c r="B85" t="n">
+        <v>8444</v>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E85" t="n">
+        <v>106554</v>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Björksplintborre</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>Scolytus ratzeburgii</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr"/>
+      <c r="J85" t="inlineStr"/>
+      <c r="K85" t="inlineStr"/>
+      <c r="L85" t="inlineStr"/>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N85" t="inlineStr"/>
+      <c r="P85" t="inlineStr">
+        <is>
+          <t>Långesjön, nordost om, Vg</t>
+        </is>
+      </c>
+      <c r="Q85" t="n">
+        <v>344117</v>
+      </c>
+      <c r="R85" t="n">
+        <v>6434282</v>
+      </c>
+      <c r="S85" t="n">
+        <v>5</v>
+      </c>
+      <c r="T85" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U85" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V85" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W85" t="inlineStr">
+        <is>
+          <t>Hålanda</t>
+        </is>
+      </c>
+      <c r="Y85" t="inlineStr">
+        <is>
+          <t>2024-04-15</t>
+        </is>
+      </c>
+      <c r="Z85" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AA85" t="inlineStr">
+        <is>
+          <t>2024-04-15</t>
+        </is>
+      </c>
+      <c r="AB85" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AC85" t="inlineStr">
+        <is>
+          <t>Rader med hål efter björksplintborren i en 4 m hög björkhögstubbe.</t>
+        </is>
+      </c>
+      <c r="AD85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF85" t="inlineStr"/>
+      <c r="AG85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT85" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>Thomas Grönlund</t>
+        </is>
+      </c>
+      <c r="AX85" t="inlineStr">
+        <is>
+          <t>Thomas Grönlund</t>
+        </is>
+      </c>
+      <c r="AY85" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>116015595</v>
+      </c>
+      <c r="B86" t="n">
+        <v>8444</v>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E86" t="n">
+        <v>106554</v>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>Björksplintborre</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>Scolytus ratzeburgii</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr"/>
+      <c r="J86" t="inlineStr"/>
+      <c r="K86" t="inlineStr"/>
+      <c r="L86" t="inlineStr"/>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N86" t="inlineStr"/>
+      <c r="P86" t="inlineStr">
+        <is>
+          <t>Långesjön, nordost om, Vg</t>
+        </is>
+      </c>
+      <c r="Q86" t="n">
+        <v>344107</v>
+      </c>
+      <c r="R86" t="n">
+        <v>6434285</v>
+      </c>
+      <c r="S86" t="n">
+        <v>5</v>
+      </c>
+      <c r="T86" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U86" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V86" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W86" t="inlineStr">
+        <is>
+          <t>Hålanda</t>
+        </is>
+      </c>
+      <c r="Y86" t="inlineStr">
+        <is>
+          <t>2024-04-15</t>
+        </is>
+      </c>
+      <c r="Z86" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AA86" t="inlineStr">
+        <is>
+          <t>2024-04-15</t>
+        </is>
+      </c>
+      <c r="AB86" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AC86" t="inlineStr">
+        <is>
+          <t>Rader med hål efter björksplintborren i en 6 m hög björkhögstubbe.</t>
+        </is>
+      </c>
+      <c r="AD86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF86" t="inlineStr"/>
+      <c r="AG86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT86" t="inlineStr"/>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>Thomas Grönlund</t>
+        </is>
+      </c>
+      <c r="AX86" t="inlineStr">
+        <is>
+          <t>Thomas Grönlund</t>
+        </is>
+      </c>
+      <c r="AY86" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>116015609</v>
+      </c>
+      <c r="B87" t="n">
+        <v>8444</v>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E87" t="n">
+        <v>106554</v>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>Björksplintborre</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>Scolytus ratzeburgii</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr"/>
+      <c r="J87" t="inlineStr"/>
+      <c r="K87" t="inlineStr"/>
+      <c r="L87" t="inlineStr"/>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N87" t="inlineStr"/>
+      <c r="P87" t="inlineStr">
+        <is>
+          <t>Långesjön, nordost om, Vg</t>
+        </is>
+      </c>
+      <c r="Q87" t="n">
+        <v>344051</v>
+      </c>
+      <c r="R87" t="n">
+        <v>6434289</v>
+      </c>
+      <c r="S87" t="n">
+        <v>5</v>
+      </c>
+      <c r="T87" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U87" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V87" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W87" t="inlineStr">
+        <is>
+          <t>Hålanda</t>
+        </is>
+      </c>
+      <c r="Y87" t="inlineStr">
+        <is>
+          <t>2024-04-15</t>
+        </is>
+      </c>
+      <c r="Z87" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AA87" t="inlineStr">
+        <is>
+          <t>2024-04-15</t>
+        </is>
+      </c>
+      <c r="AB87" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AC87" t="inlineStr">
+        <is>
+          <t>Rader med hål efter björksplintborren i en 4 m hög björkhögstubbe.</t>
+        </is>
+      </c>
+      <c r="AD87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF87" t="inlineStr"/>
+      <c r="AG87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT87" t="inlineStr"/>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>Thomas Grönlund</t>
+        </is>
+      </c>
+      <c r="AX87" t="inlineStr">
+        <is>
+          <t>Thomas Grönlund</t>
+        </is>
+      </c>
+      <c r="AY87" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>116015635</v>
+      </c>
+      <c r="B88" t="n">
+        <v>8444</v>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E88" t="n">
+        <v>106554</v>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>Björksplintborre</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>Scolytus ratzeburgii</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr"/>
+      <c r="J88" t="inlineStr"/>
+      <c r="K88" t="inlineStr"/>
+      <c r="L88" t="inlineStr"/>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N88" t="inlineStr"/>
+      <c r="P88" t="inlineStr">
+        <is>
+          <t>Långesjön, nordost om, Vg</t>
+        </is>
+      </c>
+      <c r="Q88" t="n">
+        <v>343919</v>
+      </c>
+      <c r="R88" t="n">
+        <v>6434275</v>
+      </c>
+      <c r="S88" t="n">
+        <v>5</v>
+      </c>
+      <c r="T88" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U88" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V88" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W88" t="inlineStr">
+        <is>
+          <t>Hålanda</t>
+        </is>
+      </c>
+      <c r="Y88" t="inlineStr">
+        <is>
+          <t>2024-04-15</t>
+        </is>
+      </c>
+      <c r="Z88" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AA88" t="inlineStr">
+        <is>
+          <t>2024-04-15</t>
+        </is>
+      </c>
+      <c r="AB88" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AC88" t="inlineStr">
+        <is>
+          <t>Rader med hål efter björksplintborren i en 6 m hög björkhögstubbe.</t>
+        </is>
+      </c>
+      <c r="AD88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF88" t="inlineStr"/>
+      <c r="AG88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT88" t="inlineStr"/>
+      <c r="AW88" t="inlineStr">
+        <is>
+          <t>Thomas Grönlund</t>
+        </is>
+      </c>
+      <c r="AX88" t="inlineStr">
+        <is>
+          <t>Thomas Grönlund</t>
+        </is>
+      </c>
+      <c r="AY88" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>116015654</v>
+      </c>
+      <c r="B89" t="n">
+        <v>8444</v>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E89" t="n">
+        <v>106554</v>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>Björksplintborre</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>Scolytus ratzeburgii</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr"/>
+      <c r="J89" t="inlineStr"/>
+      <c r="K89" t="inlineStr"/>
+      <c r="L89" t="inlineStr"/>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N89" t="inlineStr"/>
+      <c r="P89" t="inlineStr">
+        <is>
+          <t>Långesjön, nordost om, Vg</t>
+        </is>
+      </c>
+      <c r="Q89" t="n">
+        <v>343919</v>
+      </c>
+      <c r="R89" t="n">
+        <v>6434319</v>
+      </c>
+      <c r="S89" t="n">
+        <v>5</v>
+      </c>
+      <c r="T89" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U89" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V89" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W89" t="inlineStr">
+        <is>
+          <t>Hålanda</t>
+        </is>
+      </c>
+      <c r="Y89" t="inlineStr">
+        <is>
+          <t>2024-04-15</t>
+        </is>
+      </c>
+      <c r="Z89" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AA89" t="inlineStr">
+        <is>
+          <t>2024-04-15</t>
+        </is>
+      </c>
+      <c r="AB89" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AC89" t="inlineStr">
+        <is>
+          <t>Rader med hål efter björksplintborren i en 5 m hög björkhögstubbe.</t>
+        </is>
+      </c>
+      <c r="AD89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF89" t="inlineStr"/>
+      <c r="AG89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT89" t="inlineStr"/>
+      <c r="AW89" t="inlineStr">
+        <is>
+          <t>Thomas Grönlund</t>
+        </is>
+      </c>
+      <c r="AX89" t="inlineStr">
+        <is>
+          <t>Thomas Grönlund</t>
+        </is>
+      </c>
+      <c r="AY89" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>116015720</v>
+      </c>
+      <c r="B90" t="n">
+        <v>8444</v>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E90" t="n">
+        <v>106554</v>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>Björksplintborre</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>Scolytus ratzeburgii</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr"/>
+      <c r="J90" t="inlineStr"/>
+      <c r="K90" t="inlineStr"/>
+      <c r="L90" t="inlineStr"/>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N90" t="inlineStr"/>
+      <c r="P90" t="inlineStr">
+        <is>
+          <t>Långesjön, nordost om, Vg</t>
+        </is>
+      </c>
+      <c r="Q90" t="n">
+        <v>343857</v>
+      </c>
+      <c r="R90" t="n">
+        <v>6434254</v>
+      </c>
+      <c r="S90" t="n">
+        <v>5</v>
+      </c>
+      <c r="T90" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U90" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V90" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W90" t="inlineStr">
+        <is>
+          <t>Hålanda</t>
+        </is>
+      </c>
+      <c r="Y90" t="inlineStr">
+        <is>
+          <t>2024-04-15</t>
+        </is>
+      </c>
+      <c r="Z90" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AA90" t="inlineStr">
+        <is>
+          <t>2024-04-15</t>
+        </is>
+      </c>
+      <c r="AB90" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AC90" t="inlineStr">
+        <is>
+          <t>Rader med hål efter björksplintborren i en 3 m hög björkhögstubbe.</t>
+        </is>
+      </c>
+      <c r="AD90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF90" t="inlineStr"/>
+      <c r="AG90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT90" t="inlineStr"/>
+      <c r="AW90" t="inlineStr">
+        <is>
+          <t>Thomas Grönlund</t>
+        </is>
+      </c>
+      <c r="AX90" t="inlineStr">
+        <is>
+          <t>Thomas Grönlund</t>
+        </is>
+      </c>
+      <c r="AY90" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>116015868</v>
+      </c>
+      <c r="B91" t="n">
+        <v>8444</v>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E91" t="n">
+        <v>106554</v>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>Björksplintborre</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>Scolytus ratzeburgii</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr"/>
+      <c r="J91" t="inlineStr"/>
+      <c r="K91" t="inlineStr"/>
+      <c r="L91" t="inlineStr"/>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N91" t="inlineStr"/>
+      <c r="P91" t="inlineStr">
+        <is>
+          <t>Långesjön, nordost om, Vg</t>
+        </is>
+      </c>
+      <c r="Q91" t="n">
+        <v>343952</v>
+      </c>
+      <c r="R91" t="n">
+        <v>6434174</v>
+      </c>
+      <c r="S91" t="n">
+        <v>5</v>
+      </c>
+      <c r="T91" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U91" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V91" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W91" t="inlineStr">
+        <is>
+          <t>Hålanda</t>
+        </is>
+      </c>
+      <c r="Y91" t="inlineStr">
+        <is>
+          <t>2024-04-15</t>
+        </is>
+      </c>
+      <c r="Z91" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AA91" t="inlineStr">
+        <is>
+          <t>2024-04-15</t>
+        </is>
+      </c>
+      <c r="AB91" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AC91" t="inlineStr">
+        <is>
+          <t>Rader med hål efter björksplintborren i två björkhögstubbar.</t>
+        </is>
+      </c>
+      <c r="AD91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF91" t="inlineStr"/>
+      <c r="AG91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT91" t="inlineStr"/>
+      <c r="AW91" t="inlineStr">
+        <is>
+          <t>Thomas Grönlund</t>
+        </is>
+      </c>
+      <c r="AX91" t="inlineStr">
+        <is>
+          <t>Thomas Grönlund</t>
+        </is>
+      </c>
+      <c r="AY91" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>119447789</v>
+      </c>
+      <c r="B92" t="n">
+        <v>56884</v>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E92" t="n">
+        <v>208255</v>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>Skogsödla</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>Zootoca vivipara</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>(Jacquin, 1787)</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr"/>
+      <c r="K92" t="inlineStr"/>
+      <c r="L92" t="inlineStr"/>
+      <c r="M92" t="inlineStr"/>
+      <c r="N92" t="inlineStr"/>
+      <c r="P92" t="inlineStr">
+        <is>
+          <t>Ovanför klyftan östsidan, N Ledningsmossen, Drängedalen, Vg</t>
+        </is>
+      </c>
+      <c r="Q92" t="n">
+        <v>343851</v>
+      </c>
+      <c r="R92" t="n">
+        <v>6434288</v>
+      </c>
+      <c r="S92" t="n">
+        <v>25</v>
+      </c>
+      <c r="T92" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U92" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V92" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W92" t="inlineStr">
+        <is>
+          <t>Hålanda</t>
+        </is>
+      </c>
+      <c r="Y92" t="inlineStr">
+        <is>
+          <t>2024-08-12</t>
+        </is>
+      </c>
+      <c r="Z92" t="inlineStr">
+        <is>
+          <t>15:25</t>
+        </is>
+      </c>
+      <c r="AA92" t="inlineStr">
+        <is>
+          <t>2024-08-12</t>
+        </is>
+      </c>
+      <c r="AB92" t="inlineStr">
+        <is>
+          <t>15:25</t>
+        </is>
+      </c>
+      <c r="AD92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF92" t="inlineStr"/>
+      <c r="AG92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT92" t="inlineStr"/>
+      <c r="AW92" t="inlineStr">
+        <is>
+          <t>Ola Freijd</t>
+        </is>
+      </c>
+      <c r="AX92" t="inlineStr">
+        <is>
+          <t>Ola Freijd</t>
+        </is>
+      </c>
+      <c r="AY92" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 9045-2024 artfynd.xlsx
+++ b/artfynd/A 9045-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY92"/>
+  <dimension ref="A1:AZ92"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -787,6 +792,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115587629</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -899,6 +909,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115511988</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1024,6 +1039,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116013525</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1139,6 +1159,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116022204</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1264,6 +1289,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117123406</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1374,6 +1404,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117148040</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1481,6 +1516,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120419793</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1596,6 +1636,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116021736</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1721,6 +1766,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117123446</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1846,6 +1896,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117123515</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1963,6 +2018,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119447676</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2074,6 +2134,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115511970</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2188,6 +2253,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115587680</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2298,6 +2368,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115587706</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2408,6 +2483,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116012585</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2528,6 +2608,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116013939</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2648,6 +2733,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116014729</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2768,6 +2858,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116016843</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2888,6 +2983,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116017288</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -3002,6 +3102,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116021537</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3122,6 +3227,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119447415</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3242,6 +3352,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119447662</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3362,6 +3477,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119447781</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3482,6 +3602,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119447788</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3592,6 +3717,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120408243</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3716,6 +3846,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118756709</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3831,6 +3966,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116541309</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3951,6 +4091,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116541350</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -4071,6 +4216,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116541360</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -4186,6 +4336,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116950327</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4301,6 +4456,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116950430</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4421,6 +4581,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116950473</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4536,6 +4701,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116950486</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4651,6 +4821,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117106978</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4766,6 +4941,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117107082</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4876,6 +5056,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117146123</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4986,6 +5171,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117148586</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -5110,6 +5300,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117551193</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -5225,6 +5420,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118207826</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -5340,6 +5540,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118208072</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5455,6 +5660,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118756857</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5583,6 +5793,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119447783</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5698,6 +5913,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123819752</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5810,6 +6030,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116030367</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5932,6 +6157,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119447428</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -6054,6 +6284,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118755601</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -6176,6 +6411,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119447773</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -6293,6 +6533,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120391898</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -6410,6 +6655,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120391922</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -6527,6 +6777,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120391963</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6642,6 +6897,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117137881</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6757,6 +7017,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117552948</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6876,6 +7141,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118756349</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6990,6 +7260,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116012544</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -7105,6 +7380,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116013101</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -7224,6 +7504,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120419699</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -7339,6 +7624,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118207885</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -7458,6 +7748,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118756005</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -7577,6 +7872,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118756024</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -7692,6 +7992,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119446914</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -7811,6 +8116,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119447229</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -7935,6 +8245,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119447332</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -8050,6 +8365,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120392393</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -8165,6 +8485,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120392432</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -8289,6 +8614,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120419416</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -8404,6 +8734,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123819731</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -8518,6 +8853,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116021691</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -8633,6 +8973,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120408289</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -8753,6 +9098,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123819735</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -8865,6 +9215,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116012504</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -8987,6 +9342,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116018293</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -9109,6 +9469,11 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116018500</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -9231,6 +9596,11 @@
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116018541</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -9353,6 +9723,11 @@
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116018621</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -9460,6 +9835,11 @@
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116021091</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -9582,6 +9962,11 @@
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119447432</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -9694,6 +10079,11 @@
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120408193</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -9806,6 +10196,11 @@
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120419661</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -9914,6 +10309,11 @@
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115941784</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -10036,6 +10436,11 @@
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116015266</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -10158,6 +10563,11 @@
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116015307</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -10280,6 +10690,11 @@
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116015428</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -10402,6 +10817,11 @@
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116015501</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -10524,6 +10944,11 @@
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116015532</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -10646,6 +11071,11 @@
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116015595</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -10768,6 +11198,11 @@
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116015609</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -10890,6 +11325,11 @@
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116015635</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -11012,6 +11452,11 @@
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116015654</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -11134,6 +11579,11 @@
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116015720</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -11256,6 +11706,11 @@
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116015868</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -11373,8 +11828,106 @@
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119447789</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ92" r:id="rId91"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>